--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_20_41.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_20_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3696120.645420212</v>
+        <v>3670896.610490424</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13527545.67911028</v>
+        <v>13528220.18605883</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13527545.67911028</v>
+        <v>13528220.18605883</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9112561.819838058</v>
+        <v>9107326.161438063</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9112561.819838058</v>
+        <v>9107326.161438063</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43044419.65301387</v>
+        <v>43041576.9850283</v>
       </c>
     </row>
   </sheetData>
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
@@ -666,13 +666,13 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>402.9372717845037</v>
+        <v>2.93727178450365</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>399.6108044321707</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -681,13 +681,13 @@
         <v>440.4380012199647</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>370.6801407035176</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>305.456114391392</v>
       </c>
       <c r="M2" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -699,13 +699,13 @@
         <v>357.3555826537468</v>
       </c>
       <c r="Q2" t="n">
-        <v>201.1362550949098</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>199.3629606373397</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>85.70091195155655</v>
       </c>
       <c r="T2" t="n">
         <v>183.0855917788151</v>
@@ -714,16 +714,16 @@
         <v>249.1556885084096</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
         <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>150.8729372552541</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>202.0188387215372</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,31 +778,31 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>117.0677933923664</v>
       </c>
       <c r="R3" t="n">
-        <v>24.27446350212057</v>
+        <v>475</v>
       </c>
       <c r="S3" t="n">
-        <v>58.41362260612073</v>
+        <v>458.4136226061207</v>
       </c>
       <c r="T3" t="n">
         <v>403.5891237080799</v>
       </c>
       <c r="U3" t="n">
-        <v>400.1814918356584</v>
+        <v>0.1814918356584485</v>
       </c>
       <c r="V3" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
-        <v>19.86273944538755</v>
+        <v>49.44196359973879</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -894,10 +894,10 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>449.4745782429939</v>
+        <v>233.7571180130894</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
         <v>4.363289606868648</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>2.93727178450365</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>118.464235059569</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>440.4380012199647</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>345.5819899497487</v>
+        <v>210.5887550949095</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -936,13 +936,13 @@
         <v>357.3555826537468</v>
       </c>
       <c r="Q5" t="n">
-        <v>330.554265145161</v>
+        <v>465.5475</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>76.16012760131787</v>
+        <v>303.9664483981355</v>
       </c>
       <c r="T5" t="n">
         <v>183.0855917788151</v>
@@ -951,7 +951,7 @@
         <v>249.1556885084096</v>
       </c>
       <c r="V5" t="n">
-        <v>130.8775336295141</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
         <v>238.3734759809475</v>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -988,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>327.9302758656664</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>202.0188387215372</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,31 +1015,31 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>117.0677933923664</v>
       </c>
       <c r="R6" t="n">
-        <v>475</v>
+        <v>120.0301746508699</v>
       </c>
       <c r="S6" t="n">
         <v>58.41362260612073</v>
       </c>
       <c r="T6" t="n">
-        <v>403.5891237080799</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.1814918356584485</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>259.6198172666383</v>
       </c>
       <c r="W6" t="n">
-        <v>48.61529966248429</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>237.0294834009616</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1146,25 +1146,25 @@
         <v>2.93727178450365</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>45.53837788966423</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>118.464235059569</v>
       </c>
       <c r="J8" t="n">
         <v>10.13326463380798</v>
       </c>
       <c r="K8" t="n">
-        <v>165.8934916810661</v>
+        <v>370.6801407035177</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>345.5819899497487</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>475</v>
+        <v>390.1788610277998</v>
       </c>
       <c r="O8" t="n">
         <v>407.0701610313789</v>
@@ -1173,10 +1173,10 @@
         <v>357.3555826537468</v>
       </c>
       <c r="Q8" t="n">
-        <v>465.5475</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>127.4683344207901</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>76.16012760131787</v>
@@ -1188,7 +1188,7 @@
         <v>249.1556885084096</v>
       </c>
       <c r="V8" t="n">
-        <v>229.8510241668239</v>
+        <v>475</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
@@ -1197,7 +1197,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>475</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1213,13 +1213,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>61.09192703267516</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>475</v>
+        <v>120.0301746508699</v>
       </c>
       <c r="S9" t="n">
         <v>58.41362260612073</v>
@@ -1267,16 +1267,16 @@
         <v>0.1814918356584485</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X9" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>303.635681617385</v>
       </c>
     </row>
     <row r="10">
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26.31051432862127</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1377,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>33.46327341584126</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>133.9372717845037</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1416,13 +1416,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>207.1601276013179</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>314.0855917788151</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>380.1556885084096</v>
       </c>
       <c r="V11" t="n">
         <v>360.8510241668239</v>
@@ -1532,7 +1532,7 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>11.98090483695654</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1559,19 +1559,19 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>205.0840734590834</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>373.955831754507</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>441.0614066696756</v>
+        <v>278.6740963867578</v>
       </c>
       <c r="S13" t="n">
         <v>86.96252888318331</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>18.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>106.0804135633121</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>180.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>141.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>135.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>135.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>133.9372717845037</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>130.6108044321706</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,25 +1653,25 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>95.63238610433608</v>
       </c>
       <c r="T14" t="n">
         <v>314.0855917788151</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>380.1556885084096</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>360.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>369.3734759809475</v>
       </c>
       <c r="X14" t="n">
         <v>323.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>242.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>99.85556258400868</v>
       </c>
       <c r="M16" t="n">
-        <v>58.1685561918171</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1802,10 +1802,10 @@
         <v>319.4489739150805</v>
       </c>
       <c r="P16" t="n">
-        <v>373.955831754507</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>332.2688253623154</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1851,13 +1851,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>134.8896287080119</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>130.6108044321706</v>
+        <v>129.6108044321706</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1890,25 +1890,25 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>207.1601276013179</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>314.0855917788151</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>380.1556885084096</v>
+        <v>294.8174005685718</v>
       </c>
       <c r="V17" t="n">
-        <v>360.8510241668239</v>
+        <v>359.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>368.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>323.2818334606677</v>
+        <v>322.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>127.2349300517951</v>
+        <v>241.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -1918,25 +1918,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>115.5565566463266</v>
+        <v>114.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>92.09991244551929</v>
+        <v>91.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>78.93768689770263</v>
+        <v>77.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>73.67209722191262</v>
+        <v>72.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>70.63624233787687</v>
+        <v>69.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>56.30074342219716</v>
+        <v>55.30074342219716</v>
       </c>
       <c r="H18" t="n">
-        <v>58.93027586566642</v>
+        <v>57.93027586566642</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1966,28 +1966,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>251.0301746508699</v>
+        <v>250.0301746508699</v>
       </c>
       <c r="S18" t="n">
-        <v>189.4136226061207</v>
+        <v>188.4136226061207</v>
       </c>
       <c r="T18" t="n">
-        <v>134.5891237080799</v>
+        <v>133.5891237080799</v>
       </c>
       <c r="U18" t="n">
-        <v>131.1814918356584</v>
+        <v>130.1814918356584</v>
       </c>
       <c r="V18" t="n">
-        <v>145.5106671915202</v>
+        <v>144.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>163.3731429098285</v>
+        <v>162.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>150.8627394453875</v>
+        <v>149.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>130.3913927661343</v>
+        <v>129.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2000,16 +2000,16 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>3.725246648044674</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>5.382855967741932</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -2027,10 +2027,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3.938608988752073</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>193.9664966484515</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2039,16 +2039,16 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>372.955831754507</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>388.4185301068975</v>
       </c>
       <c r="R19" t="n">
-        <v>441.0614066696756</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>86.96252888318331</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2079,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>179.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>206.1601276013179</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>313.0855917788151</v>
@@ -2136,16 +2136,16 @@
         <v>379.1556885084096</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>359.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>209.6663477249893</v>
+        <v>368.3734759809475</v>
       </c>
       <c r="X20" t="n">
         <v>322.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>241.3174326828064</v>
+        <v>108.3939861043361</v>
       </c>
     </row>
     <row r="21">
@@ -2267,22 +2267,22 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>192.9664966484515</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>244.8911080585701</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>318.4489739150805</v>
       </c>
       <c r="P22" t="n">
-        <v>306.0514043049205</v>
+        <v>372.955831754507</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>69.96955619181699</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>17.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2316,19 +2316,19 @@
         <v>211.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>179.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>140.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>134.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>132.9372717845037</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2364,19 +2364,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>206.1601276013179</v>
       </c>
       <c r="T23" t="n">
-        <v>313.0855917788151</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>379.1556885084096</v>
       </c>
       <c r="V23" t="n">
-        <v>297.9438569431722</v>
+        <v>264.66098402795</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>368.3734759809475</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>69.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>55.30074342219717</v>
+        <v>55.30074342219716</v>
       </c>
       <c r="H24" t="n">
-        <v>57.93027586566643</v>
+        <v>57.93027586566642</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>336.3390954358065</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>425.035266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>250.3765665526232</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>85.96252888318331</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2550,22 +2550,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>266.9993129555745</v>
+        <v>269.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>234.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>198.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>189.3632896068686</v>
+        <v>192.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>189.8896287080119</v>
+        <v>192.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>190.9372717845037</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>153.703881822797</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2610,16 +2610,16 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>410.275508522385</v>
       </c>
       <c r="W26" t="n">
-        <v>423.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>296.3174326828064</v>
+        <v>299.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2629,25 +2629,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>169.5565566463266</v>
+        <v>172.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>149.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>132.9376868977026</v>
+        <v>135.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>127.6720972219126</v>
+        <v>130.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>127.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>110.3007434221972</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>112.9302758656664</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>60.68368950388155</v>
       </c>
       <c r="S27" t="n">
-        <v>125.6784215349728</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>188.5891237080799</v>
+        <v>191.5891237080799</v>
       </c>
       <c r="U27" t="n">
-        <v>185.1814918356584</v>
+        <v>188.1814918356584</v>
       </c>
       <c r="V27" t="n">
-        <v>199.5106671915202</v>
+        <v>202.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>217.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>207.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>184.3913927661343</v>
+        <v>187.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>10.50043757702846</v>
+        <v>13.50043757702846</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2741,13 +2741,13 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>250.9664966484515</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>41.26811373187938</v>
       </c>
       <c r="O28" t="n">
-        <v>312.9361103803309</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>11.37280983870968</v>
+        <v>14.37280983870968</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2787,25 +2787,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>190.1763804096178</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>183.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>144.3391557398498</v>
       </c>
       <c r="E29" t="n">
         <v>138.3632896068686</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>138.8896287080119</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>133.6108044321707</v>
+        <v>133.6108044321706</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,19 +2844,19 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>383.1556885084096</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>372.3734759809475</v>
+        <v>233.684749525313</v>
       </c>
       <c r="X29" t="n">
         <v>326.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>245.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2881,10 +2881,10 @@
         <v>73.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>59.30074342219717</v>
+        <v>59.30074342219716</v>
       </c>
       <c r="H30" t="n">
-        <v>61.93027586566643</v>
+        <v>61.93027586566642</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         <v>254.0301746508699</v>
       </c>
       <c r="S30" t="n">
-        <v>59.04935265531923</v>
+        <v>192.4136226061207</v>
       </c>
       <c r="T30" t="n">
         <v>137.5891237080799</v>
@@ -2929,7 +2929,7 @@
         <v>148.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>166.3731429098285</v>
+        <v>33.00887295902731</v>
       </c>
       <c r="X30" t="n">
         <v>153.8627394453875</v>
@@ -2945,19 +2945,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>21.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>6.725246648044674</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>19.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>14.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>8.382855967741932</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2975,16 +2975,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>102.8555625840087</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>248.8911080585701</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>322.4489739150805</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>444.0614066696756</v>
+        <v>150.8302798877541</v>
       </c>
       <c r="S31" t="n">
-        <v>83.04901391288074</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>21.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3030,16 +3030,16 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>144.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>138.3632896068686</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>138.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>136.9372717845037</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>133.6108044321706</v>
@@ -3075,25 +3075,25 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>210.1601276013179</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>383.1556885084096</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>363.8510241668239</v>
+        <v>254.9459793886772</v>
       </c>
       <c r="W32" t="n">
         <v>372.3734759809475</v>
       </c>
       <c r="X32" t="n">
-        <v>154.0332075258267</v>
+        <v>326.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>245.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -3109,7 +3109,7 @@
         <v>95.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>81.93768689770263</v>
       </c>
       <c r="E33" t="n">
         <v>76.67209722191262</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>254.0301746508699</v>
+        <v>120.6659047000684</v>
       </c>
       <c r="S33" t="n">
         <v>192.4136226061207</v>
@@ -3172,7 +3172,7 @@
         <v>153.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>81.96480971303575</v>
+        <v>133.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>21.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>19.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -3221,19 +3221,19 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>322.4489739150805</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>429.035266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>252.4850770431725</v>
+        <v>309.758859063141</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>89.96252888318331</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3267,19 +3267,19 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>144.3391557398498</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>138.8896287080119</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>136.9372717845037</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>133.6108044321707</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3312,22 +3312,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>210.1601276013179</v>
       </c>
       <c r="T35" t="n">
-        <v>308.459577883151</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
         <v>383.1556885084096</v>
       </c>
       <c r="V35" t="n">
-        <v>363.8510241668239</v>
+        <v>234.6554472447889</v>
       </c>
       <c r="W35" t="n">
         <v>372.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>326.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -3349,16 +3349,16 @@
         <v>81.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>76.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>73.63624233787687</v>
       </c>
       <c r="G36" t="n">
-        <v>59.30074342219716</v>
+        <v>59.30074342219717</v>
       </c>
       <c r="H36" t="n">
-        <v>61.93027586566642</v>
+        <v>61.93027586566643</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3391,7 +3391,7 @@
         <v>254.0301746508699</v>
       </c>
       <c r="S36" t="n">
-        <v>192.4136226061207</v>
+        <v>135.7214498772322</v>
       </c>
       <c r="T36" t="n">
         <v>137.5891237080799</v>
@@ -3403,7 +3403,7 @@
         <v>148.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>33.00887295902731</v>
+        <v>166.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>153.8627394453875</v>
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>21.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>19.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -3449,28 +3449,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>102.8555625840087</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>196.9664966484515</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>22.76555619181711</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>322.4489739150805</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>376.955831754507</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>291.735755353127</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>89.96252888318331</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>215.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>73.41898471008145</v>
+        <v>183.4745782429939</v>
       </c>
       <c r="D38" t="n">
         <v>144.3391557398498</v>
@@ -3516,7 +3516,7 @@
         <v>136.9372717845037</v>
       </c>
       <c r="H38" t="n">
-        <v>133.6108044321706</v>
+        <v>133.6108044321707</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3549,10 +3549,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>210.1601276013179</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>317.0855917788151</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3561,10 +3561,10 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>90.90829238655282</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>326.2818334606677</v>
       </c>
       <c r="Y38" t="n">
         <v>245.3174326828064</v>
@@ -3586,16 +3586,16 @@
         <v>81.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>76.67209722191262</v>
       </c>
       <c r="F39" t="n">
         <v>73.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>59.30074342219716</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>61.93027586566642</v>
+        <v>61.93027586566643</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3625,10 +3625,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>197.3380019219815</v>
+        <v>254.0301746508699</v>
       </c>
       <c r="S39" t="n">
-        <v>192.4136226061207</v>
+        <v>118.3500960775164</v>
       </c>
       <c r="T39" t="n">
         <v>137.5891237080799</v>
@@ -3659,10 +3659,10 @@
         <v>21.11380033707866</v>
       </c>
       <c r="C40" t="n">
-        <v>6.725246648044674</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>19.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -3698,16 +3698,16 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>121.4389149616567</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>429.035266425598</v>
+        <v>42.71171053799591</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>444.0614066696756</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>89.96252888318332</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>397.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>66.46423505956903</v>
+        <v>63.46423505956903</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,28 +3783,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>147.3629606373397</v>
+        <v>144.3629606373397</v>
       </c>
       <c r="S41" t="n">
-        <v>424.1601276013179</v>
+        <v>188.5328043030801</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>266.65969845877</v>
+        <v>450.000000000004</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>450.0000000000034</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>452.0000000000093</v>
+        <v>450.0000000000035</v>
       </c>
     </row>
     <row r="42">
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>258.9097844269875</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>272.9302758656664</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>65.06779339236638</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>450.0000000000049</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>299.056317497421</v>
       </c>
       <c r="T42" t="n">
-        <v>351.5891237080799</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>348.1814918356584</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>362.5106671915202</v>
+        <v>359.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>367.8627394453875</v>
+        <v>364.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>41.8888653901891</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>44.8291653901891</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>450.0000000000025</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>448.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>409.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>401.9372717845037</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -4020,13 +4020,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>198.3629606373397</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>450.0000000000034</v>
       </c>
       <c r="T44" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4035,13 +4035,13 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>169.2563767787378</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>280.4211866974309</v>
       </c>
     </row>
     <row r="45">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>383.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -4066,13 +4066,13 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>324.3007434221972</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>201.0188387215372</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,31 +4096,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>116.0677933923664</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>180.6460927647458</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>399.1814918356584</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>413.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>431.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>225.8105409042975</v>
+        <v>418.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>398.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>868.8377230699333</v>
+        <v>514.3785136509076</v>
       </c>
       <c r="C2" t="n">
-        <v>868.8377230699333</v>
+        <v>464.404192193338</v>
       </c>
       <c r="D2" t="n">
-        <v>858.3941314135194</v>
+        <v>453.9606005369241</v>
       </c>
       <c r="E2" t="n">
-        <v>853.9867681742581</v>
+        <v>449.5532372976628</v>
       </c>
       <c r="F2" t="n">
-        <v>445.0073452368724</v>
+        <v>444.6142184006811</v>
       </c>
       <c r="G2" t="n">
-        <v>38</v>
+        <v>441.6472772042128</v>
       </c>
       <c r="H2" t="n">
         <v>38</v>
@@ -4324,49 +4324,49 @@
         <v>63.36313008084375</v>
       </c>
       <c r="K2" t="n">
-        <v>533.6131300808437</v>
+        <v>159.188745531836</v>
       </c>
       <c r="L2" t="n">
-        <v>1003.863130080844</v>
+        <v>320.8972158435613</v>
       </c>
       <c r="M2" t="n">
-        <v>994.3151502828639</v>
+        <v>791.1472158435613</v>
       </c>
       <c r="N2" t="n">
-        <v>1464.565150282864</v>
+        <v>1261.397215843561</v>
       </c>
       <c r="O2" t="n">
-        <v>1523.633169443087</v>
+        <v>1320.465235003785</v>
       </c>
       <c r="P2" t="n">
-        <v>1632.917934439303</v>
+        <v>1429.75</v>
       </c>
       <c r="Q2" t="n">
         <v>1900</v>
       </c>
       <c r="R2" t="n">
-        <v>1698.623272083495</v>
+        <v>1900</v>
       </c>
       <c r="S2" t="n">
-        <v>1698.623272083495</v>
+        <v>1813.433422271155</v>
       </c>
       <c r="T2" t="n">
-        <v>1513.688330892773</v>
+        <v>1628.498481080433</v>
       </c>
       <c r="U2" t="n">
-        <v>1262.015918258016</v>
+        <v>1376.826068445675</v>
       </c>
       <c r="V2" t="n">
-        <v>1262.015918258016</v>
+        <v>1144.653316762015</v>
       </c>
       <c r="W2" t="n">
-        <v>1021.234629388372</v>
+        <v>903.8720278923709</v>
       </c>
       <c r="X2" t="n">
-        <v>868.8377230699333</v>
+        <v>709.6479536896762</v>
       </c>
       <c r="Y2" t="n">
-        <v>868.8377230699333</v>
+        <v>597.2061024949223</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>333.7597926835222</v>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>333.7597926835222</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>333.7597926835222</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>333.7597926835222</v>
       </c>
       <c r="F3" t="n">
-        <v>38</v>
+        <v>333.7597926835222</v>
       </c>
       <c r="G3" t="n">
-        <v>38</v>
+        <v>333.7597926835222</v>
       </c>
       <c r="H3" t="n">
-        <v>38</v>
+        <v>333.7597926835222</v>
       </c>
       <c r="I3" t="n">
-        <v>38</v>
+        <v>129.7003596314643</v>
       </c>
       <c r="J3" t="n">
-        <v>202.9982216847329</v>
+        <v>294.6985813161972</v>
       </c>
       <c r="K3" t="n">
-        <v>462.3378426847767</v>
+        <v>554.038202316241</v>
       </c>
       <c r="L3" t="n">
-        <v>828.0093401290335</v>
+        <v>919.7096997604978</v>
       </c>
       <c r="M3" t="n">
-        <v>1024.158081871893</v>
+        <v>1115.858441503357</v>
       </c>
       <c r="N3" t="n">
-        <v>1270.41974421531</v>
+        <v>1362.120103846774</v>
       </c>
       <c r="O3" t="n">
-        <v>1612.818083823557</v>
+        <v>1704.518443455021</v>
       </c>
       <c r="P3" t="n">
-        <v>1808.299640368536</v>
+        <v>1900</v>
       </c>
       <c r="Q3" t="n">
-        <v>1808.299640368536</v>
+        <v>1781.749703644074</v>
       </c>
       <c r="R3" t="n">
-        <v>1783.779980265384</v>
+        <v>1301.951723846094</v>
       </c>
       <c r="S3" t="n">
-        <v>1724.776321067282</v>
+        <v>838.9076606075886</v>
       </c>
       <c r="T3" t="n">
-        <v>1317.110539543969</v>
+        <v>431.2418790842756</v>
       </c>
       <c r="U3" t="n">
-        <v>912.886810417041</v>
+        <v>431.0585539977519</v>
       </c>
       <c r="V3" t="n">
-        <v>494.1891667892428</v>
+        <v>416.4013144103578</v>
       </c>
       <c r="W3" t="n">
-        <v>461.4890224358807</v>
+        <v>383.7011700569957</v>
       </c>
       <c r="X3" t="n">
-        <v>441.4256492587216</v>
+        <v>333.7597926835222</v>
       </c>
       <c r="Y3" t="n">
-        <v>38</v>
+        <v>333.7597926835222</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="C4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="E4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="G4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="H4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="I4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="J4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="K4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="L4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="M4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="N4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="O4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="P4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="Q4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="R4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="S4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="T4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="U4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="V4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="W4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="X4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
       <c r="Y4" t="n">
-        <v>38</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="5">
@@ -4534,25 +4534,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>623.9888923251991</v>
+        <v>293.9082748159794</v>
       </c>
       <c r="C5" t="n">
-        <v>169.9741668272254</v>
+        <v>57.78997379265686</v>
       </c>
       <c r="D5" t="n">
-        <v>169.9741668272254</v>
+        <v>47.34638213624293</v>
       </c>
       <c r="E5" t="n">
-        <v>165.5668035879642</v>
+        <v>42.93901889698167</v>
       </c>
       <c r="F5" t="n">
-        <v>160.6277846909825</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>157.6608434945142</v>
+        <v>38</v>
       </c>
       <c r="H5" t="n">
-        <v>157.6608434945142</v>
+        <v>38</v>
       </c>
       <c r="I5" t="n">
         <v>38</v>
@@ -4564,19 +4564,19 @@
         <v>533.6131300808437</v>
       </c>
       <c r="L5" t="n">
-        <v>654.7904129598853</v>
+        <v>791.1472158435613</v>
       </c>
       <c r="M5" t="n">
-        <v>1125.040412959885</v>
+        <v>1261.397215843561</v>
       </c>
       <c r="N5" t="n">
-        <v>1595.290412959885</v>
+        <v>1731.647215843561</v>
       </c>
       <c r="O5" t="n">
-        <v>1654.358432120109</v>
+        <v>1790.715235003785</v>
       </c>
       <c r="P5" t="n">
-        <v>1763.643197116324</v>
+        <v>1900</v>
       </c>
       <c r="Q5" t="n">
         <v>1900</v>
@@ -4585,25 +4585,25 @@
         <v>1900</v>
       </c>
       <c r="S5" t="n">
-        <v>1823.070578180487</v>
+        <v>1592.963183436227</v>
       </c>
       <c r="T5" t="n">
-        <v>1638.135636989765</v>
+        <v>1408.028242245504</v>
       </c>
       <c r="U5" t="n">
-        <v>1386.463224355007</v>
+        <v>1156.355829610747</v>
       </c>
       <c r="V5" t="n">
-        <v>1254.263695436306</v>
+        <v>924.1830779270867</v>
       </c>
       <c r="W5" t="n">
-        <v>1013.482406566662</v>
+        <v>683.4017890574428</v>
       </c>
       <c r="X5" t="n">
-        <v>819.2583323639677</v>
+        <v>489.177714854748</v>
       </c>
       <c r="Y5" t="n">
-        <v>706.8164811692138</v>
+        <v>376.7358636599941</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>573.3021359466704</v>
+        <v>402.7473863086054</v>
       </c>
       <c r="C6" t="n">
-        <v>573.3021359466704</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>573.3021359466704</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>573.3021359466704</v>
+        <v>38</v>
       </c>
       <c r="F6" t="n">
-        <v>573.3021359466704</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>573.3021359466704</v>
+        <v>38</v>
       </c>
       <c r="H6" t="n">
-        <v>242.0594330520578</v>
+        <v>38</v>
       </c>
       <c r="I6" t="n">
         <v>38</v>
@@ -4658,31 +4658,31 @@
         <v>1808.299640368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1808.299640368536</v>
+        <v>1690.04934401261</v>
       </c>
       <c r="R6" t="n">
-        <v>1328.501660570556</v>
+        <v>1568.806743355166</v>
       </c>
       <c r="S6" t="n">
-        <v>1269.498001372454</v>
+        <v>1509.803084157064</v>
       </c>
       <c r="T6" t="n">
-        <v>861.832219849141</v>
+        <v>1509.803084157064</v>
       </c>
       <c r="U6" t="n">
-        <v>861.832219849141</v>
+        <v>1509.61975907054</v>
       </c>
       <c r="V6" t="n">
-        <v>861.832219849141</v>
+        <v>1247.377519407269</v>
       </c>
       <c r="W6" t="n">
-        <v>812.7258565537023</v>
+        <v>1214.677375053907</v>
       </c>
       <c r="X6" t="n">
-        <v>812.7258565537023</v>
+        <v>1194.614001876748</v>
       </c>
       <c r="Y6" t="n">
-        <v>573.3021359466704</v>
+        <v>791.1883526180262</v>
       </c>
     </row>
     <row r="7">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>110.7312364466948</v>
+        <v>276.3904414459203</v>
       </c>
       <c r="C8" t="n">
-        <v>60.75691498912519</v>
+        <v>226.4161199883507</v>
       </c>
       <c r="D8" t="n">
-        <v>50.31332333271126</v>
+        <v>215.9725283319368</v>
       </c>
       <c r="E8" t="n">
-        <v>45.90596009345001</v>
+        <v>211.5651650926755</v>
       </c>
       <c r="F8" t="n">
-        <v>40.96694119646833</v>
+        <v>206.6261461956938</v>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>203.6592049992255</v>
       </c>
       <c r="H8" t="n">
-        <v>38</v>
+        <v>157.6608434945142</v>
       </c>
       <c r="I8" t="n">
         <v>38</v>
@@ -4798,49 +4798,49 @@
         <v>498.0143791577697</v>
       </c>
       <c r="K8" t="n">
-        <v>800.6951956415413</v>
+        <v>593.8399946087619</v>
       </c>
       <c r="L8" t="n">
-        <v>1270.945195641541</v>
+        <v>715.0172774878035</v>
       </c>
       <c r="M8" t="n">
-        <v>1741.195195641541</v>
+        <v>1185.267277487804</v>
       </c>
       <c r="N8" t="n">
-        <v>1731.647215843561</v>
+        <v>1261.397215843561</v>
       </c>
       <c r="O8" t="n">
-        <v>1790.715235003785</v>
+        <v>1320.465235003785</v>
       </c>
       <c r="P8" t="n">
-        <v>1900</v>
+        <v>1429.75</v>
       </c>
       <c r="Q8" t="n">
         <v>1900</v>
       </c>
       <c r="R8" t="n">
-        <v>1771.244106645667</v>
+        <v>1900</v>
       </c>
       <c r="S8" t="n">
-        <v>1694.314684826154</v>
+        <v>1823.070578180487</v>
       </c>
       <c r="T8" t="n">
-        <v>1509.379743635431</v>
+        <v>1638.135636989765</v>
       </c>
       <c r="U8" t="n">
-        <v>1257.707331000674</v>
+        <v>1386.463224355007</v>
       </c>
       <c r="V8" t="n">
-        <v>1025.534579317013</v>
+        <v>906.6652445570276</v>
       </c>
       <c r="W8" t="n">
-        <v>784.7532904473694</v>
+        <v>665.8839556873836</v>
       </c>
       <c r="X8" t="n">
-        <v>590.5292162446747</v>
+        <v>471.6598814846889</v>
       </c>
       <c r="Y8" t="n">
-        <v>110.7312364466948</v>
+        <v>359.218030289935</v>
       </c>
     </row>
     <row r="9">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>794.2281376447017</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>794.2281376447017</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
-        <v>442.7759286571233</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
-        <v>381.0669114524009</v>
+        <v>38</v>
       </c>
       <c r="F9" t="n">
         <v>38</v>
@@ -4898,28 +4898,28 @@
         <v>1808.299640368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1328.501660570556</v>
+        <v>1687.057039711091</v>
       </c>
       <c r="S9" t="n">
-        <v>1269.498001372454</v>
+        <v>1628.05338051299</v>
       </c>
       <c r="T9" t="n">
-        <v>1265.872623889545</v>
+        <v>1624.428003030081</v>
       </c>
       <c r="U9" t="n">
-        <v>1265.689298803021</v>
+        <v>1624.244677943557</v>
       </c>
       <c r="V9" t="n">
-        <v>1251.032059215627</v>
+        <v>1205.547034315759</v>
       </c>
       <c r="W9" t="n">
-        <v>1218.331914862265</v>
+        <v>768.8064859219926</v>
       </c>
       <c r="X9" t="n">
-        <v>794.2281376447017</v>
+        <v>344.7027087044294</v>
       </c>
       <c r="Y9" t="n">
-        <v>794.2281376447017</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>207.0914597983282</v>
       </c>
       <c r="C11" t="n">
-        <v>38</v>
+        <v>207.0914597983282</v>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>207.0914597983282</v>
       </c>
       <c r="E11" t="n">
-        <v>38</v>
+        <v>207.0914597983282</v>
       </c>
       <c r="F11" t="n">
-        <v>38</v>
+        <v>173.2901735197007</v>
       </c>
       <c r="G11" t="n">
         <v>38</v>
@@ -5032,25 +5032,25 @@
         <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>498.2180680125301</v>
+        <v>72.21637879223495</v>
       </c>
       <c r="K11" t="n">
-        <v>968.46806801253</v>
+        <v>542.4663787922349</v>
       </c>
       <c r="L11" t="n">
-        <v>1096.591897962279</v>
+        <v>1012.716378792235</v>
       </c>
       <c r="M11" t="n">
-        <v>1246.031486248274</v>
+        <v>1482.966378792235</v>
       </c>
       <c r="N11" t="n">
-        <v>1246.031486248274</v>
+        <v>1716.281486248274</v>
       </c>
       <c r="O11" t="n">
-        <v>1313.282026827209</v>
+        <v>1783.532026827209</v>
       </c>
       <c r="P11" t="n">
-        <v>1429.75</v>
+        <v>1900</v>
       </c>
       <c r="Q11" t="n">
         <v>1900</v>
@@ -5059,25 +5059,25 @@
         <v>1900</v>
       </c>
       <c r="S11" t="n">
-        <v>1690.747345857255</v>
+        <v>1900</v>
       </c>
       <c r="T11" t="n">
-        <v>1373.4891723433</v>
+        <v>1900</v>
       </c>
       <c r="U11" t="n">
-        <v>1373.4891723433</v>
+        <v>1516.004355042011</v>
       </c>
       <c r="V11" t="n">
-        <v>1008.993188336407</v>
+        <v>1151.508371035118</v>
       </c>
       <c r="W11" t="n">
-        <v>635.8886671435307</v>
+        <v>778.4038498422415</v>
       </c>
       <c r="X11" t="n">
-        <v>309.3413606176037</v>
+        <v>451.8565433163145</v>
       </c>
       <c r="Y11" t="n">
-        <v>64.57627709961744</v>
+        <v>207.0914597983282</v>
       </c>
     </row>
     <row r="12">
@@ -5108,28 +5108,28 @@
         <v>38</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>104.3113496656782</v>
       </c>
       <c r="J12" t="n">
-        <v>202.9982216847329</v>
+        <v>269.3095713504111</v>
       </c>
       <c r="K12" t="n">
-        <v>462.3378426847767</v>
+        <v>528.6491923504549</v>
       </c>
       <c r="L12" t="n">
-        <v>828.0093401290335</v>
+        <v>894.3206897947116</v>
       </c>
       <c r="M12" t="n">
-        <v>1024.158081871893</v>
+        <v>1090.469431537571</v>
       </c>
       <c r="N12" t="n">
-        <v>1270.41974421531</v>
+        <v>1336.731093880988</v>
       </c>
       <c r="O12" t="n">
-        <v>1612.818083823557</v>
+        <v>1679.129433489235</v>
       </c>
       <c r="P12" t="n">
-        <v>1808.299640368536</v>
+        <v>1874.610990034214</v>
       </c>
       <c r="Q12" t="n">
         <v>1899.096838334143</v>
@@ -5166,52 +5166,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>328.8440525657294</v>
+        <v>347.4959241308429</v>
       </c>
       <c r="C13" t="n">
-        <v>328.8440525657294</v>
+        <v>347.4959241308429</v>
       </c>
       <c r="D13" t="n">
-        <v>328.8440525657294</v>
+        <v>347.4959241308429</v>
       </c>
       <c r="E13" t="n">
-        <v>328.8440525657294</v>
+        <v>335.394000053109</v>
       </c>
       <c r="F13" t="n">
-        <v>328.8440525657294</v>
+        <v>335.394000053109</v>
       </c>
       <c r="G13" t="n">
-        <v>352.9248086165491</v>
+        <v>359.4747561039287</v>
       </c>
       <c r="H13" t="n">
-        <v>395.9893754152909</v>
+        <v>402.5393229026705</v>
       </c>
       <c r="I13" t="n">
-        <v>498.3844458267837</v>
+        <v>504.9343933141632</v>
       </c>
       <c r="J13" t="n">
-        <v>755.526431069399</v>
+        <v>762.0763785567785</v>
       </c>
       <c r="K13" t="n">
-        <v>778.5131404161034</v>
+        <v>785.0630879034829</v>
       </c>
       <c r="L13" t="n">
-        <v>778.5131404161034</v>
+        <v>785.0630879034829</v>
       </c>
       <c r="M13" t="n">
-        <v>778.5131404161034</v>
+        <v>785.0630879034829</v>
       </c>
       <c r="N13" t="n">
-        <v>571.3575106594535</v>
+        <v>785.0630879034829</v>
       </c>
       <c r="O13" t="n">
-        <v>571.3575106594535</v>
+        <v>785.0630879034829</v>
       </c>
       <c r="P13" t="n">
-        <v>571.3575106594535</v>
+        <v>407.329924515092</v>
       </c>
       <c r="Q13" t="n">
-        <v>571.3575106594535</v>
+        <v>407.329924515092</v>
       </c>
       <c r="R13" t="n">
         <v>125.8409382658417</v>
@@ -5235,7 +5235,7 @@
         <v>347.4959241308429</v>
       </c>
       <c r="Y13" t="n">
-        <v>328.8440525657294</v>
+        <v>347.4959241308429</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>904.2775035498976</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>721.9799497690956</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>579.2131257894494</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>442.4825302269557</v>
+        <v>38</v>
       </c>
       <c r="F14" t="n">
-        <v>305.2202790067417</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>169.930105487041</v>
+        <v>38</v>
       </c>
       <c r="H14" t="n">
         <v>38</v>
@@ -5281,13 +5281,13 @@
         <v>1199.868558665796</v>
       </c>
       <c r="N14" t="n">
-        <v>1246.031486248274</v>
+        <v>1670.118558665796</v>
       </c>
       <c r="O14" t="n">
-        <v>1313.282026827209</v>
+        <v>1737.369099244731</v>
       </c>
       <c r="P14" t="n">
-        <v>1429.75</v>
+        <v>1853.837072417522</v>
       </c>
       <c r="Q14" t="n">
         <v>1900</v>
@@ -5296,25 +5296,25 @@
         <v>1900</v>
       </c>
       <c r="S14" t="n">
-        <v>1900</v>
+        <v>1803.40163019764</v>
       </c>
       <c r="T14" t="n">
-        <v>1582.741826486045</v>
+        <v>1486.143456683686</v>
       </c>
       <c r="U14" t="n">
-        <v>1582.741826486045</v>
+        <v>1102.147811725696</v>
       </c>
       <c r="V14" t="n">
-        <v>1582.741826486045</v>
+        <v>737.6518277188034</v>
       </c>
       <c r="W14" t="n">
-        <v>1582.741826486045</v>
+        <v>364.547306525927</v>
       </c>
       <c r="X14" t="n">
-        <v>1256.194519960118</v>
+        <v>38</v>
       </c>
       <c r="Y14" t="n">
-        <v>1011.429436442132</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -5345,28 +5345,28 @@
         <v>38</v>
       </c>
       <c r="I15" t="n">
-        <v>38</v>
+        <v>104.3113496656782</v>
       </c>
       <c r="J15" t="n">
-        <v>202.9982216847329</v>
+        <v>269.3095713504111</v>
       </c>
       <c r="K15" t="n">
-        <v>462.3378426847767</v>
+        <v>528.6491923504549</v>
       </c>
       <c r="L15" t="n">
-        <v>828.0093401290335</v>
+        <v>894.3206897947116</v>
       </c>
       <c r="M15" t="n">
-        <v>1024.158081871893</v>
+        <v>1090.469431537571</v>
       </c>
       <c r="N15" t="n">
-        <v>1361.216942180917</v>
+        <v>1336.731093880988</v>
       </c>
       <c r="O15" t="n">
-        <v>1703.615281789164</v>
+        <v>1679.129433489235</v>
       </c>
       <c r="P15" t="n">
-        <v>1899.096838334143</v>
+        <v>1874.610990034214</v>
       </c>
       <c r="Q15" t="n">
         <v>1899.096838334143</v>
@@ -5433,19 +5433,19 @@
         <v>797.1650119812168</v>
       </c>
       <c r="L16" t="n">
-        <v>797.1650119812168</v>
+        <v>696.300807350905</v>
       </c>
       <c r="M16" t="n">
-        <v>738.408894615745</v>
+        <v>696.300807350905</v>
       </c>
       <c r="N16" t="n">
-        <v>738.408894615745</v>
+        <v>696.300807350905</v>
       </c>
       <c r="O16" t="n">
-        <v>415.7331633883909</v>
+        <v>373.6250761235509</v>
       </c>
       <c r="P16" t="n">
-        <v>38</v>
+        <v>373.6250761235509</v>
       </c>
       <c r="Q16" t="n">
         <v>38</v>
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>169.930105487041</v>
+        <v>305.332154687053</v>
       </c>
       <c r="C17" t="n">
-        <v>169.930105487041</v>
+        <v>305.332154687053</v>
       </c>
       <c r="D17" t="n">
-        <v>169.930105487041</v>
+        <v>305.332154687053</v>
       </c>
       <c r="E17" t="n">
-        <v>169.930105487041</v>
+        <v>305.332154687053</v>
       </c>
       <c r="F17" t="n">
-        <v>169.930105487041</v>
+        <v>169.08000447694</v>
       </c>
       <c r="G17" t="n">
-        <v>169.930105487041</v>
+        <v>169.08000447694</v>
       </c>
       <c r="H17" t="n">
-        <v>38</v>
+        <v>38.16</v>
       </c>
       <c r="I17" t="n">
-        <v>38</v>
+        <v>38.16</v>
       </c>
       <c r="J17" t="n">
-        <v>72.21637879223495</v>
+        <v>498.3780680125301</v>
       </c>
       <c r="K17" t="n">
-        <v>542.4663787922349</v>
+        <v>970.60806801253</v>
       </c>
       <c r="L17" t="n">
-        <v>670.5902087419836</v>
+        <v>1098.731897962279</v>
       </c>
       <c r="M17" t="n">
-        <v>1140.840208741984</v>
+        <v>1252.051486248274</v>
       </c>
       <c r="N17" t="n">
-        <v>1611.090208741984</v>
+        <v>1252.051486248274</v>
       </c>
       <c r="O17" t="n">
-        <v>1678.340749320919</v>
+        <v>1319.302026827209</v>
       </c>
       <c r="P17" t="n">
-        <v>1794.808722493709</v>
+        <v>1435.77</v>
       </c>
       <c r="Q17" t="n">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="R17" t="n">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="S17" t="n">
-        <v>1690.747345857255</v>
+        <v>1908</v>
       </c>
       <c r="T17" t="n">
-        <v>1373.4891723433</v>
+        <v>1908</v>
       </c>
       <c r="U17" t="n">
-        <v>989.4935273853105</v>
+        <v>1610.204645890331</v>
       </c>
       <c r="V17" t="n">
-        <v>624.9975433784176</v>
+        <v>1246.71876289354</v>
       </c>
       <c r="W17" t="n">
-        <v>624.9975433784176</v>
+        <v>874.6243427107643</v>
       </c>
       <c r="X17" t="n">
-        <v>298.4502368524906</v>
+        <v>549.0871371949384</v>
       </c>
       <c r="Y17" t="n">
-        <v>169.930105487041</v>
+        <v>305.332154687053</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>472.9262203948232</v>
+        <v>467.0256143342172</v>
       </c>
       <c r="C18" t="n">
-        <v>379.8960058033896</v>
+        <v>375.0055007528846</v>
       </c>
       <c r="D18" t="n">
-        <v>300.1609685329829</v>
+        <v>296.2805644925789</v>
       </c>
       <c r="E18" t="n">
-        <v>225.7447087128691</v>
+        <v>222.8744056825661</v>
       </c>
       <c r="F18" t="n">
-        <v>154.39496897764</v>
+        <v>152.534766957438</v>
       </c>
       <c r="G18" t="n">
-        <v>97.52553117744083</v>
+        <v>96.67543016733981</v>
       </c>
       <c r="H18" t="n">
-        <v>38</v>
+        <v>38.16</v>
       </c>
       <c r="I18" t="n">
-        <v>38</v>
+        <v>38.16</v>
       </c>
       <c r="J18" t="n">
-        <v>202.9982216847329</v>
+        <v>203.1582216847329</v>
       </c>
       <c r="K18" t="n">
-        <v>462.3378426847767</v>
+        <v>462.4978426847767</v>
       </c>
       <c r="L18" t="n">
-        <v>918.8065380946406</v>
+        <v>828.1693401290335</v>
       </c>
       <c r="M18" t="n">
-        <v>1114.9552798375</v>
+        <v>1024.318081871893</v>
       </c>
       <c r="N18" t="n">
-        <v>1361.216942180917</v>
+        <v>1270.57974421531</v>
       </c>
       <c r="O18" t="n">
-        <v>1703.615281789164</v>
+        <v>1612.978083823557</v>
       </c>
       <c r="P18" t="n">
-        <v>1899.096838334143</v>
+        <v>1808.459640368535</v>
       </c>
       <c r="Q18" t="n">
-        <v>1899.096838334143</v>
+        <v>1884.105323182627</v>
       </c>
       <c r="R18" t="n">
-        <v>1645.531005353466</v>
+        <v>1631.549591212052</v>
       </c>
       <c r="S18" t="n">
-        <v>1454.204113832132</v>
+        <v>1441.232800700819</v>
       </c>
       <c r="T18" t="n">
-        <v>1318.255504025991</v>
+        <v>1306.294291904779</v>
       </c>
       <c r="U18" t="n">
-        <v>1185.748946616235</v>
+        <v>1174.797835505124</v>
       </c>
       <c r="V18" t="n">
-        <v>1038.768474705608</v>
+        <v>1028.827464604598</v>
       </c>
       <c r="W18" t="n">
-        <v>873.7450980290137</v>
+        <v>864.8141889381046</v>
       </c>
       <c r="X18" t="n">
-        <v>721.3584925286222</v>
+        <v>713.4376844478141</v>
       </c>
       <c r="Y18" t="n">
-        <v>589.6500149870723</v>
+        <v>582.7393079163653</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>347.4959241308429</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="C19" t="n">
-        <v>343.7330487287775</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="D19" t="n">
-        <v>327.0297981676104</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="E19" t="n">
-        <v>327.0297981676104</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="F19" t="n">
-        <v>321.5925699173659</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="G19" t="n">
-        <v>345.6733259681856</v>
+        <v>377.6766801816625</v>
       </c>
       <c r="H19" t="n">
-        <v>388.7378927669275</v>
+        <v>421.7312469804043</v>
       </c>
       <c r="I19" t="n">
-        <v>491.1329631784203</v>
+        <v>525.116317391897</v>
       </c>
       <c r="J19" t="n">
-        <v>748.2749484210356</v>
+        <v>783.2483026345124</v>
       </c>
       <c r="K19" t="n">
-        <v>771.26165776774</v>
+        <v>807.2250119812168</v>
       </c>
       <c r="L19" t="n">
-        <v>767.2832648498086</v>
+        <v>807.2250119812168</v>
       </c>
       <c r="M19" t="n">
-        <v>571.3575106594535</v>
+        <v>807.2250119812168</v>
       </c>
       <c r="N19" t="n">
-        <v>571.3575106594535</v>
+        <v>807.2250119812168</v>
       </c>
       <c r="O19" t="n">
-        <v>571.3575106594535</v>
+        <v>807.2250119812168</v>
       </c>
       <c r="P19" t="n">
-        <v>571.3575106594535</v>
+        <v>430.5019496029268</v>
       </c>
       <c r="Q19" t="n">
-        <v>571.3575106594535</v>
+        <v>38.16</v>
       </c>
       <c r="R19" t="n">
-        <v>125.8409382658417</v>
+        <v>38.16</v>
       </c>
       <c r="S19" t="n">
-        <v>38</v>
+        <v>38.16</v>
       </c>
       <c r="T19" t="n">
-        <v>97.9417644047065</v>
+        <v>99.09176440470651</v>
       </c>
       <c r="U19" t="n">
-        <v>214.8228219610259</v>
+        <v>216.962821961026</v>
       </c>
       <c r="V19" t="n">
-        <v>283.9542148469719</v>
+        <v>287.0842148469719</v>
       </c>
       <c r="W19" t="n">
-        <v>326.1551331066493</v>
+        <v>330.2751331066493</v>
       </c>
       <c r="X19" t="n">
-        <v>347.4959241308429</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="Y19" t="n">
-        <v>347.4959241308429</v>
+        <v>352.6059241308428</v>
       </c>
     </row>
     <row r="20">
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>219.4474527707009</v>
+        <v>38.16</v>
       </c>
       <c r="C20" t="n">
         <v>38.16</v>
@@ -5743,25 +5743,25 @@
         <v>38.16</v>
       </c>
       <c r="J20" t="n">
-        <v>498.3780680125301</v>
+        <v>72.37637879223496</v>
       </c>
       <c r="K20" t="n">
-        <v>601.6547287160477</v>
+        <v>544.6063787922349</v>
       </c>
       <c r="L20" t="n">
-        <v>729.7785586657964</v>
+        <v>672.7302087419836</v>
       </c>
       <c r="M20" t="n">
-        <v>1202.008558665796</v>
+        <v>1144.960208741984</v>
       </c>
       <c r="N20" t="n">
-        <v>1252.051486248274</v>
+        <v>1144.960208741984</v>
       </c>
       <c r="O20" t="n">
-        <v>1319.302026827209</v>
+        <v>1617.190208741984</v>
       </c>
       <c r="P20" t="n">
-        <v>1435.77</v>
+        <v>1733.658181914775</v>
       </c>
       <c r="Q20" t="n">
         <v>1908</v>
@@ -5770,25 +5770,25 @@
         <v>1908</v>
       </c>
       <c r="S20" t="n">
-        <v>1699.757446867356</v>
+        <v>1908</v>
       </c>
       <c r="T20" t="n">
-        <v>1383.509374363502</v>
+        <v>1591.751927496146</v>
       </c>
       <c r="U20" t="n">
-        <v>1000.523830415613</v>
+        <v>1208.766383548258</v>
       </c>
       <c r="V20" t="n">
-        <v>1000.523830415613</v>
+        <v>845.280500551466</v>
       </c>
       <c r="W20" t="n">
-        <v>788.7396407944121</v>
+        <v>473.1860803686907</v>
       </c>
       <c r="X20" t="n">
-        <v>463.2024352785862</v>
+        <v>147.6488748528648</v>
       </c>
       <c r="Y20" t="n">
-        <v>219.4474527707009</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="21">
@@ -5822,25 +5822,25 @@
         <v>38.16</v>
       </c>
       <c r="J21" t="n">
-        <v>278.8039044988249</v>
+        <v>203.1582216847329</v>
       </c>
       <c r="K21" t="n">
-        <v>538.1435254988687</v>
+        <v>462.4978426847767</v>
       </c>
       <c r="L21" t="n">
-        <v>903.8150229431254</v>
+        <v>828.1693401290335</v>
       </c>
       <c r="M21" t="n">
-        <v>1099.963764685985</v>
+        <v>1024.318081871893</v>
       </c>
       <c r="N21" t="n">
-        <v>1346.225427029402</v>
+        <v>1270.57974421531</v>
       </c>
       <c r="O21" t="n">
-        <v>1688.623766637649</v>
+        <v>1612.978083823557</v>
       </c>
       <c r="P21" t="n">
-        <v>1884.105323182627</v>
+        <v>1808.459640368535</v>
       </c>
       <c r="Q21" t="n">
         <v>1884.105323182627</v>
@@ -5877,52 +5877,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>334.9641535758303</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="C22" t="n">
-        <v>334.9641535758303</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="D22" t="n">
-        <v>334.9641535758303</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="E22" t="n">
-        <v>334.9641535758303</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="F22" t="n">
-        <v>334.9641535758303</v>
+        <v>352.6059241308428</v>
       </c>
       <c r="G22" t="n">
-        <v>360.03490962665</v>
+        <v>377.6766801816625</v>
       </c>
       <c r="H22" t="n">
-        <v>404.0894764253918</v>
+        <v>421.7312469804043</v>
       </c>
       <c r="I22" t="n">
-        <v>507.4745468368845</v>
+        <v>525.116317391897</v>
       </c>
       <c r="J22" t="n">
-        <v>765.6065320794999</v>
+        <v>783.2483026345124</v>
       </c>
       <c r="K22" t="n">
-        <v>789.5832414262043</v>
+        <v>807.2250119812168</v>
       </c>
       <c r="L22" t="n">
-        <v>789.5832414262043</v>
+        <v>807.2250119812168</v>
       </c>
       <c r="M22" t="n">
-        <v>594.6675882459501</v>
+        <v>807.2250119812168</v>
       </c>
       <c r="N22" t="n">
-        <v>347.3028326312328</v>
+        <v>807.2250119812168</v>
       </c>
       <c r="O22" t="n">
-        <v>347.3028326312328</v>
+        <v>485.5593817639637</v>
       </c>
       <c r="P22" t="n">
-        <v>38.16</v>
+        <v>108.8363193856737</v>
       </c>
       <c r="Q22" t="n">
-        <v>38.16</v>
+        <v>108.8363193856737</v>
       </c>
       <c r="R22" t="n">
         <v>38.16</v>
@@ -5946,7 +5946,7 @@
         <v>352.6059241308428</v>
       </c>
       <c r="Y22" t="n">
-        <v>334.9641535758303</v>
+        <v>352.6059241308428</v>
       </c>
     </row>
     <row r="23">
@@ -5956,19 +5956,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>449.9172900315374</v>
+        <v>219.4474527707009</v>
       </c>
       <c r="C23" t="n">
-        <v>449.9172900315374</v>
+        <v>38.16</v>
       </c>
       <c r="D23" t="n">
-        <v>308.1605670619922</v>
+        <v>38.16</v>
       </c>
       <c r="E23" t="n">
-        <v>172.4400725095996</v>
+        <v>38.16</v>
       </c>
       <c r="F23" t="n">
-        <v>172.4400725095996</v>
+        <v>38.16</v>
       </c>
       <c r="G23" t="n">
         <v>38.16</v>
@@ -5980,16 +5980,16 @@
         <v>38.16</v>
       </c>
       <c r="J23" t="n">
-        <v>498.3780680125301</v>
+        <v>72.37637879223496</v>
       </c>
       <c r="K23" t="n">
-        <v>601.6547287160477</v>
+        <v>544.6063787922349</v>
       </c>
       <c r="L23" t="n">
-        <v>729.7785586657964</v>
+        <v>672.7302087419836</v>
       </c>
       <c r="M23" t="n">
-        <v>1202.008558665796</v>
+        <v>1144.960208741984</v>
       </c>
       <c r="N23" t="n">
         <v>1252.051486248274</v>
@@ -6007,25 +6007,25 @@
         <v>1908</v>
       </c>
       <c r="S23" t="n">
-        <v>1908</v>
+        <v>1699.757446867356</v>
       </c>
       <c r="T23" t="n">
-        <v>1591.751927496146</v>
+        <v>1699.757446867356</v>
       </c>
       <c r="U23" t="n">
-        <v>1208.766383548258</v>
+        <v>1316.771902919467</v>
       </c>
       <c r="V23" t="n">
-        <v>907.8129926965687</v>
+        <v>1049.437575618507</v>
       </c>
       <c r="W23" t="n">
-        <v>907.8129926965687</v>
+        <v>677.3431554357321</v>
       </c>
       <c r="X23" t="n">
-        <v>907.8129926965687</v>
+        <v>677.3431554357321</v>
       </c>
       <c r="Y23" t="n">
-        <v>664.0580101886834</v>
+        <v>433.5881729278469</v>
       </c>
     </row>
     <row r="24">
@@ -6050,34 +6050,34 @@
         <v>152.534766957438</v>
       </c>
       <c r="G24" t="n">
-        <v>96.67543016733984</v>
+        <v>96.67543016733981</v>
       </c>
       <c r="H24" t="n">
         <v>38.16</v>
       </c>
       <c r="I24" t="n">
-        <v>38.16</v>
+        <v>105.4613496656782</v>
       </c>
       <c r="J24" t="n">
-        <v>278.8039044988249</v>
+        <v>270.4595713504111</v>
       </c>
       <c r="K24" t="n">
-        <v>538.1435254988687</v>
+        <v>529.7991923504549</v>
       </c>
       <c r="L24" t="n">
-        <v>903.8150229431254</v>
+        <v>895.4706897947116</v>
       </c>
       <c r="M24" t="n">
-        <v>1099.963764685985</v>
+        <v>1091.619431537571</v>
       </c>
       <c r="N24" t="n">
-        <v>1346.225427029402</v>
+        <v>1337.881093880988</v>
       </c>
       <c r="O24" t="n">
-        <v>1688.623766637649</v>
+        <v>1680.279433489235</v>
       </c>
       <c r="P24" t="n">
-        <v>1884.105323182627</v>
+        <v>1875.760990034214</v>
       </c>
       <c r="Q24" t="n">
         <v>1884.105323182627</v>
@@ -6156,13 +6156,13 @@
         <v>807.2250119812168</v>
       </c>
       <c r="P25" t="n">
-        <v>467.4885519450486</v>
+        <v>807.2250119812168</v>
       </c>
       <c r="Q25" t="n">
-        <v>38.16</v>
+        <v>377.8964600361682</v>
       </c>
       <c r="R25" t="n">
-        <v>38.16</v>
+        <v>124.9908372557407</v>
       </c>
       <c r="S25" t="n">
         <v>38.16</v>
@@ -6193,19 +6193,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>656.0867641998732</v>
+        <v>818.5128745850849</v>
       </c>
       <c r="C26" t="n">
-        <v>419.2437558736167</v>
+        <v>818.5128745850849</v>
       </c>
       <c r="D26" t="n">
-        <v>419.2437558736167</v>
+        <v>618.170293029681</v>
       </c>
       <c r="E26" t="n">
-        <v>227.9677057656685</v>
+        <v>423.8639398914298</v>
       </c>
       <c r="F26" t="n">
-        <v>36.16</v>
+        <v>229.0259310954582</v>
       </c>
       <c r="G26" t="n">
         <v>36.16</v>
@@ -6217,25 +6217,25 @@
         <v>36.16</v>
       </c>
       <c r="J26" t="n">
-        <v>70.37637879223496</v>
+        <v>483.6400000000012</v>
       </c>
       <c r="K26" t="n">
-        <v>173.6530394957526</v>
+        <v>586.9166607035188</v>
       </c>
       <c r="L26" t="n">
-        <v>301.7768694455012</v>
+        <v>796.5720268272069</v>
       </c>
       <c r="M26" t="n">
-        <v>729.3214862482741</v>
+        <v>796.5720268272069</v>
       </c>
       <c r="N26" t="n">
-        <v>1176.801486248274</v>
+        <v>796.5720268272069</v>
       </c>
       <c r="O26" t="n">
-        <v>1244.052026827209</v>
+        <v>1244.052026827208</v>
       </c>
       <c r="P26" t="n">
-        <v>1360.52</v>
+        <v>1360.519999999999</v>
       </c>
       <c r="Q26" t="n">
         <v>1808</v>
@@ -6244,25 +6244,25 @@
         <v>1808</v>
       </c>
       <c r="S26" t="n">
-        <v>1652.743553714346</v>
+        <v>1808</v>
       </c>
       <c r="T26" t="n">
-        <v>1652.743553714346</v>
+        <v>1808</v>
       </c>
       <c r="U26" t="n">
-        <v>1652.743553714346</v>
+        <v>1808</v>
       </c>
       <c r="V26" t="n">
-        <v>1652.743553714346</v>
+        <v>1393.580294421833</v>
       </c>
       <c r="W26" t="n">
-        <v>1225.093577976015</v>
+        <v>1393.580294421833</v>
       </c>
       <c r="X26" t="n">
-        <v>1225.093577976015</v>
+        <v>1393.580294421833</v>
       </c>
       <c r="Y26" t="n">
-        <v>925.7830399125747</v>
+        <v>1091.239453328089</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>524.8880842499788</v>
+        <v>584.9942817202136</v>
       </c>
       <c r="C27" t="n">
-        <v>524.8880842499788</v>
+        <v>434.3883095530224</v>
       </c>
       <c r="D27" t="n">
-        <v>390.6075924341175</v>
+        <v>297.0775147068581</v>
       </c>
       <c r="E27" t="n">
-        <v>261.6458780685491</v>
+        <v>165.0854973109867</v>
       </c>
       <c r="F27" t="n">
-        <v>261.6458780685491</v>
+        <v>36.16</v>
       </c>
       <c r="G27" t="n">
-        <v>150.2309857228954</v>
+        <v>36.16</v>
       </c>
       <c r="H27" t="n">
         <v>36.16</v>
       </c>
       <c r="I27" t="n">
-        <v>36.16</v>
+        <v>37.70035963146432</v>
       </c>
       <c r="J27" t="n">
-        <v>201.1582216847329</v>
+        <v>202.6985813161972</v>
       </c>
       <c r="K27" t="n">
-        <v>460.4978426847767</v>
+        <v>462.038202316241</v>
       </c>
       <c r="L27" t="n">
-        <v>826.1693401290335</v>
+        <v>827.7096997604978</v>
       </c>
       <c r="M27" t="n">
-        <v>1022.318081871893</v>
+        <v>1023.858441503357</v>
       </c>
       <c r="N27" t="n">
-        <v>1268.57974421531</v>
+        <v>1270.120103846774</v>
       </c>
       <c r="O27" t="n">
-        <v>1610.978083823557</v>
+        <v>1612.518443455021</v>
       </c>
       <c r="P27" t="n">
-        <v>1806.459640368535</v>
+        <v>1808</v>
       </c>
       <c r="Q27" t="n">
         <v>1808</v>
       </c>
       <c r="R27" t="n">
-        <v>1808</v>
+        <v>1746.703343935473</v>
       </c>
       <c r="S27" t="n">
-        <v>1681.052099459623</v>
+        <v>1746.703343935473</v>
       </c>
       <c r="T27" t="n">
-        <v>1490.558035108028</v>
+        <v>1553.178976553574</v>
       </c>
       <c r="U27" t="n">
-        <v>1303.506023152817</v>
+        <v>1363.096661568061</v>
       </c>
       <c r="V27" t="n">
-        <v>1101.980096696736</v>
+        <v>1158.540432081677</v>
       </c>
       <c r="W27" t="n">
-        <v>882.4112654746868</v>
+        <v>1158.540432081677</v>
       </c>
       <c r="X27" t="n">
-        <v>882.4112654746868</v>
+        <v>948.5780690055277</v>
       </c>
       <c r="Y27" t="n">
-        <v>696.1573333876825</v>
+        <v>759.2938338882203</v>
       </c>
     </row>
     <row r="28">
@@ -6351,43 +6351,43 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>110.2465281412045</v>
+        <v>98.30622511090151</v>
       </c>
       <c r="C28" t="n">
-        <v>110.2465281412045</v>
+        <v>98.30622511090151</v>
       </c>
       <c r="D28" t="n">
-        <v>110.2465281412045</v>
+        <v>98.30622511090151</v>
       </c>
       <c r="E28" t="n">
-        <v>110.2465281412045</v>
+        <v>98.30622511090151</v>
       </c>
       <c r="F28" t="n">
-        <v>110.2465281412045</v>
+        <v>98.30622511090151</v>
       </c>
       <c r="G28" t="n">
-        <v>110.2465281412045</v>
+        <v>98.30622511090151</v>
       </c>
       <c r="H28" t="n">
-        <v>99.64002553814548</v>
+        <v>84.66941947753942</v>
       </c>
       <c r="I28" t="n">
-        <v>148.5750959496382</v>
+        <v>130.6344898890322</v>
       </c>
       <c r="J28" t="n">
-        <v>352.2570811922535</v>
+        <v>331.3464751316474</v>
       </c>
       <c r="K28" t="n">
-        <v>352.2570811922535</v>
+        <v>331.3464751316474</v>
       </c>
       <c r="L28" t="n">
-        <v>352.2570811922535</v>
+        <v>331.3464751316474</v>
       </c>
       <c r="M28" t="n">
-        <v>352.2570811922535</v>
+        <v>77.84496336553474</v>
       </c>
       <c r="N28" t="n">
-        <v>352.2570811922535</v>
+        <v>36.16</v>
       </c>
       <c r="O28" t="n">
         <v>36.16</v>
@@ -6405,22 +6405,22 @@
         <v>36.16</v>
       </c>
       <c r="T28" t="n">
-        <v>42.6417644047065</v>
+        <v>39.6717644047065</v>
       </c>
       <c r="U28" t="n">
-        <v>106.0628219610259</v>
+        <v>100.1228219610259</v>
       </c>
       <c r="V28" t="n">
-        <v>121.7342148469719</v>
+        <v>112.8242148469719</v>
       </c>
       <c r="W28" t="n">
-        <v>110.2465281412045</v>
+        <v>98.30622511090151</v>
       </c>
       <c r="X28" t="n">
-        <v>110.2465281412045</v>
+        <v>98.30622511090151</v>
       </c>
       <c r="Y28" t="n">
-        <v>110.2465281412045</v>
+        <v>98.30622511090151</v>
       </c>
     </row>
     <row r="29">
@@ -6430,16 +6430,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>310.8813071101407</v>
+        <v>782.2988451817121</v>
       </c>
       <c r="C29" t="n">
-        <v>310.8813071101407</v>
+        <v>596.9709883706071</v>
       </c>
       <c r="D29" t="n">
-        <v>310.8813071101407</v>
+        <v>451.1738613606577</v>
       </c>
       <c r="E29" t="n">
-        <v>171.1204085173441</v>
+        <v>311.4129627678611</v>
       </c>
       <c r="F29" t="n">
         <v>171.1204085173441</v>
@@ -6457,22 +6457,22 @@
         <v>70.37637879223496</v>
       </c>
       <c r="K29" t="n">
-        <v>517.856378792235</v>
+        <v>173.6530394957526</v>
       </c>
       <c r="L29" t="n">
-        <v>965.3363787922349</v>
+        <v>621.1330394957525</v>
       </c>
       <c r="M29" t="n">
-        <v>965.336378792235</v>
+        <v>1068.613039495754</v>
       </c>
       <c r="N29" t="n">
-        <v>1412.816378792235</v>
+        <v>1516.093039495755</v>
       </c>
       <c r="O29" t="n">
-        <v>1480.06691937117</v>
+        <v>1583.34358007469</v>
       </c>
       <c r="P29" t="n">
-        <v>1596.534892543961</v>
+        <v>1699.811553247481</v>
       </c>
       <c r="Q29" t="n">
         <v>1808</v>
@@ -6487,19 +6487,19 @@
         <v>1595.717042826952</v>
       </c>
       <c r="U29" t="n">
-        <v>1208.691094838659</v>
+        <v>1595.717042826952</v>
       </c>
       <c r="V29" t="n">
-        <v>1208.691094838659</v>
+        <v>1595.717042826952</v>
       </c>
       <c r="W29" t="n">
-        <v>832.5562706154797</v>
+        <v>1359.671841286231</v>
       </c>
       <c r="X29" t="n">
-        <v>502.9786610592496</v>
+        <v>1030.094231730001</v>
       </c>
       <c r="Y29" t="n">
-        <v>502.9786610592496</v>
+        <v>782.2988451817121</v>
       </c>
     </row>
     <row r="30">
@@ -6521,10 +6521,10 @@
         <v>232.9956178037783</v>
       </c>
       <c r="F30" t="n">
-        <v>158.6155750382461</v>
+        <v>158.615575038246</v>
       </c>
       <c r="G30" t="n">
-        <v>98.71583420774388</v>
+        <v>98.71583420774385</v>
       </c>
       <c r="H30" t="n">
         <v>36.16</v>
@@ -6560,16 +6560,16 @@
         <v>1551.40386398902</v>
       </c>
       <c r="S30" t="n">
-        <v>1491.758053226072</v>
+        <v>1357.046669437383</v>
       </c>
       <c r="T30" t="n">
-        <v>1352.779140389627</v>
+        <v>1218.067756600939</v>
       </c>
       <c r="U30" t="n">
-        <v>1217.242279949568</v>
+        <v>1082.53089616088</v>
       </c>
       <c r="V30" t="n">
-        <v>1067.231505008639</v>
+        <v>932.5201212199504</v>
       </c>
       <c r="W30" t="n">
         <v>899.177825301741</v>
@@ -6588,55 +6588,55 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>287.7966784878721</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="C31" t="n">
-        <v>281.0035000555038</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="D31" t="n">
-        <v>261.2699464640336</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="E31" t="n">
-        <v>246.1377193559967</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="F31" t="n">
-        <v>237.6701880754493</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="G31" t="n">
-        <v>258.780944126269</v>
+        <v>351.9166801816626</v>
       </c>
       <c r="H31" t="n">
-        <v>298.8755109250108</v>
+        <v>392.0112469804044</v>
       </c>
       <c r="I31" t="n">
-        <v>398.3005813365036</v>
+        <v>491.4363173918971</v>
       </c>
       <c r="J31" t="n">
-        <v>652.4725665791188</v>
+        <v>745.6083026345125</v>
       </c>
       <c r="K31" t="n">
-        <v>672.4892759258233</v>
+        <v>765.625011981217</v>
       </c>
       <c r="L31" t="n">
-        <v>568.5947682652085</v>
+        <v>765.625011981217</v>
       </c>
       <c r="M31" t="n">
-        <v>568.5947682652085</v>
+        <v>765.625011981217</v>
       </c>
       <c r="N31" t="n">
-        <v>568.5947682652085</v>
+        <v>514.2198523260956</v>
       </c>
       <c r="O31" t="n">
-        <v>568.5947682652085</v>
+        <v>188.5138180684385</v>
       </c>
       <c r="P31" t="n">
-        <v>568.5947682652085</v>
+        <v>188.5138180684385</v>
       </c>
       <c r="Q31" t="n">
-        <v>568.5947682652085</v>
+        <v>188.5138180684385</v>
       </c>
       <c r="R31" t="n">
-        <v>120.0478928412937</v>
+        <v>36.16</v>
       </c>
       <c r="S31" t="n">
         <v>36.16</v>
@@ -6657,7 +6657,7 @@
         <v>330.8059241308429</v>
       </c>
       <c r="Y31" t="n">
-        <v>309.1237495354263</v>
+        <v>330.8059241308429</v>
       </c>
     </row>
     <row r="32">
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>309.4408850673477</v>
+        <v>596.9709883706071</v>
       </c>
       <c r="C32" t="n">
-        <v>309.4408850673477</v>
+        <v>596.9709883706071</v>
       </c>
       <c r="D32" t="n">
-        <v>309.4408850673477</v>
+        <v>451.1738613606577</v>
       </c>
       <c r="E32" t="n">
-        <v>309.4408850673477</v>
+        <v>311.4129627678611</v>
       </c>
       <c r="F32" t="n">
-        <v>309.4408850673477</v>
+        <v>171.1204085173441</v>
       </c>
       <c r="G32" t="n">
         <v>171.1204085173441</v>
@@ -6691,25 +6691,25 @@
         <v>36.16</v>
       </c>
       <c r="J32" t="n">
-        <v>483.64</v>
+        <v>70.37637879223496</v>
       </c>
       <c r="K32" t="n">
-        <v>931.1200000000001</v>
+        <v>173.6530394957526</v>
       </c>
       <c r="L32" t="n">
-        <v>1059.243829949749</v>
+        <v>301.7768694455012</v>
       </c>
       <c r="M32" t="n">
-        <v>1506.723829949749</v>
+        <v>749.2568694455026</v>
       </c>
       <c r="N32" t="n">
-        <v>1506.723829949749</v>
+        <v>1176.801486248273</v>
       </c>
       <c r="O32" t="n">
-        <v>1573.974370528684</v>
+        <v>1244.052026827208</v>
       </c>
       <c r="P32" t="n">
-        <v>1690.442343701475</v>
+        <v>1360.519999999999</v>
       </c>
       <c r="Q32" t="n">
         <v>1808</v>
@@ -6718,25 +6718,25 @@
         <v>1808</v>
       </c>
       <c r="S32" t="n">
-        <v>1595.717042826952</v>
+        <v>1808</v>
       </c>
       <c r="T32" t="n">
-        <v>1595.717042826952</v>
+        <v>1808</v>
       </c>
       <c r="U32" t="n">
-        <v>1208.691094838659</v>
+        <v>1808</v>
       </c>
       <c r="V32" t="n">
-        <v>841.1648078014631</v>
+        <v>1550.478808698306</v>
       </c>
       <c r="W32" t="n">
-        <v>465.0299835782837</v>
+        <v>1174.343984475126</v>
       </c>
       <c r="X32" t="n">
-        <v>309.4408850673477</v>
+        <v>844.7663749188964</v>
       </c>
       <c r="Y32" t="n">
-        <v>309.4408850673477</v>
+        <v>596.9709883706071</v>
       </c>
     </row>
     <row r="33">
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>406.5026982759317</v>
+        <v>489.2680385766415</v>
       </c>
       <c r="C33" t="n">
-        <v>310.4421806541951</v>
+        <v>393.2075209549048</v>
       </c>
       <c r="D33" t="n">
         <v>310.4421806541951</v>
@@ -6767,55 +6767,55 @@
         <v>36.16</v>
       </c>
       <c r="I33" t="n">
-        <v>36.16</v>
+        <v>37.70035963146432</v>
       </c>
       <c r="J33" t="n">
-        <v>201.1582216847329</v>
+        <v>202.6985813161972</v>
       </c>
       <c r="K33" t="n">
-        <v>460.4978426847767</v>
+        <v>462.038202316241</v>
       </c>
       <c r="L33" t="n">
-        <v>826.1693401290335</v>
+        <v>827.7096997604978</v>
       </c>
       <c r="M33" t="n">
-        <v>1022.318081871893</v>
+        <v>1023.858441503357</v>
       </c>
       <c r="N33" t="n">
-        <v>1268.57974421531</v>
+        <v>1270.120103846774</v>
       </c>
       <c r="O33" t="n">
-        <v>1610.978083823557</v>
+        <v>1612.518443455021</v>
       </c>
       <c r="P33" t="n">
-        <v>1806.459640368535</v>
+        <v>1808</v>
       </c>
       <c r="Q33" t="n">
         <v>1808</v>
       </c>
       <c r="R33" t="n">
-        <v>1551.40386398902</v>
+        <v>1686.115247777709</v>
       </c>
       <c r="S33" t="n">
-        <v>1357.046669437383</v>
+        <v>1491.758053226072</v>
       </c>
       <c r="T33" t="n">
-        <v>1218.067756600939</v>
+        <v>1352.779140389627</v>
       </c>
       <c r="U33" t="n">
-        <v>1082.53089616088</v>
+        <v>1217.242279949568</v>
       </c>
       <c r="V33" t="n">
-        <v>932.5201212199504</v>
+        <v>1067.231505008639</v>
       </c>
       <c r="W33" t="n">
-        <v>764.4664415130529</v>
+        <v>899.177825301741</v>
       </c>
       <c r="X33" t="n">
-        <v>609.0495329823584</v>
+        <v>743.7609167710465</v>
       </c>
       <c r="Y33" t="n">
-        <v>526.2567958984839</v>
+        <v>609.0221361991936</v>
       </c>
     </row>
     <row r="34">
@@ -6825,55 +6825,55 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>309.4788530832886</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="C34" t="n">
-        <v>309.4788530832886</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="D34" t="n">
-        <v>289.7452994918185</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="E34" t="n">
-        <v>289.7452994918185</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="F34" t="n">
-        <v>289.7452994918185</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="G34" t="n">
-        <v>310.8560555426382</v>
+        <v>351.9166801816626</v>
       </c>
       <c r="H34" t="n">
-        <v>350.95062234138</v>
+        <v>392.0112469804044</v>
       </c>
       <c r="I34" t="n">
-        <v>450.3756927528727</v>
+        <v>491.4363173918971</v>
       </c>
       <c r="J34" t="n">
-        <v>704.547677995488</v>
+        <v>745.6083026345125</v>
       </c>
       <c r="K34" t="n">
-        <v>724.5643873421925</v>
+        <v>765.625011981217</v>
       </c>
       <c r="L34" t="n">
-        <v>724.5643873421925</v>
+        <v>765.625011981217</v>
       </c>
       <c r="M34" t="n">
-        <v>724.5643873421925</v>
+        <v>765.625011981217</v>
       </c>
       <c r="N34" t="n">
-        <v>724.5643873421925</v>
+        <v>765.625011981217</v>
       </c>
       <c r="O34" t="n">
-        <v>724.5643873421925</v>
+        <v>439.9189777235599</v>
       </c>
       <c r="P34" t="n">
-        <v>724.5643873421925</v>
+        <v>439.9189777235599</v>
       </c>
       <c r="Q34" t="n">
-        <v>291.1954313567399</v>
+        <v>439.9189777235599</v>
       </c>
       <c r="R34" t="n">
-        <v>36.16</v>
+        <v>127.0312412961448</v>
       </c>
       <c r="S34" t="n">
         <v>36.16</v>
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>36.16</v>
+        <v>595.5305663278141</v>
       </c>
       <c r="C35" t="n">
-        <v>36.16</v>
+        <v>595.5305663278141</v>
       </c>
       <c r="D35" t="n">
-        <v>36.16</v>
+        <v>449.7334393178648</v>
       </c>
       <c r="E35" t="n">
-        <v>36.16</v>
+        <v>449.7334393178648</v>
       </c>
       <c r="F35" t="n">
-        <v>36.16</v>
+        <v>309.4408850673478</v>
       </c>
       <c r="G35" t="n">
-        <v>36.16</v>
+        <v>171.1204085173441</v>
       </c>
       <c r="H35" t="n">
         <v>36.16</v>
@@ -6931,22 +6931,22 @@
         <v>70.37637879223496</v>
       </c>
       <c r="K35" t="n">
-        <v>173.6530394957526</v>
+        <v>517.856378792235</v>
       </c>
       <c r="L35" t="n">
-        <v>301.7768694455012</v>
+        <v>645.9802087419837</v>
       </c>
       <c r="M35" t="n">
-        <v>749.2568694455013</v>
+        <v>1093.460208741985</v>
       </c>
       <c r="N35" t="n">
-        <v>1176.801486248274</v>
+        <v>1176.801486248273</v>
       </c>
       <c r="O35" t="n">
-        <v>1244.052026827209</v>
+        <v>1244.052026827208</v>
       </c>
       <c r="P35" t="n">
-        <v>1360.52</v>
+        <v>1360.519999999999</v>
       </c>
       <c r="Q35" t="n">
         <v>1808</v>
@@ -6955,25 +6955,25 @@
         <v>1808</v>
       </c>
       <c r="S35" t="n">
-        <v>1808</v>
+        <v>1595.717042826952</v>
       </c>
       <c r="T35" t="n">
-        <v>1496.424668804898</v>
+        <v>1595.717042826952</v>
       </c>
       <c r="U35" t="n">
-        <v>1109.398720816605</v>
+        <v>1208.691094838659</v>
       </c>
       <c r="V35" t="n">
-        <v>741.8724337794094</v>
+        <v>971.6653905509934</v>
       </c>
       <c r="W35" t="n">
-        <v>365.73760955623</v>
+        <v>595.5305663278141</v>
       </c>
       <c r="X35" t="n">
-        <v>36.16</v>
+        <v>595.5305663278141</v>
       </c>
       <c r="Y35" t="n">
-        <v>36.16</v>
+        <v>595.5305663278141</v>
       </c>
     </row>
     <row r="36">
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>489.2680385766415</v>
+        <v>411.8214757262247</v>
       </c>
       <c r="C36" t="n">
-        <v>393.2075209549048</v>
+        <v>315.760958104488</v>
       </c>
       <c r="D36" t="n">
-        <v>310.4421806541951</v>
+        <v>232.9956178037783</v>
       </c>
       <c r="E36" t="n">
         <v>232.9956178037783</v>
       </c>
       <c r="F36" t="n">
-        <v>158.615575038246</v>
+        <v>158.6155750382461</v>
       </c>
       <c r="G36" t="n">
-        <v>98.71583420774385</v>
+        <v>98.71583420774388</v>
       </c>
       <c r="H36" t="n">
         <v>36.16</v>
@@ -7034,25 +7034,25 @@
         <v>1551.40386398902</v>
       </c>
       <c r="S36" t="n">
-        <v>1357.046669437383</v>
+        <v>1414.311490375654</v>
       </c>
       <c r="T36" t="n">
-        <v>1218.067756600939</v>
+        <v>1275.33257753921</v>
       </c>
       <c r="U36" t="n">
-        <v>1082.53089616088</v>
+        <v>1139.795717099151</v>
       </c>
       <c r="V36" t="n">
-        <v>932.5201212199504</v>
+        <v>989.7849421582216</v>
       </c>
       <c r="W36" t="n">
-        <v>899.177825301741</v>
+        <v>821.7312624513241</v>
       </c>
       <c r="X36" t="n">
-        <v>743.7609167710465</v>
+        <v>666.3143539206296</v>
       </c>
       <c r="Y36" t="n">
-        <v>609.0221361991936</v>
+        <v>531.5755733487767</v>
       </c>
     </row>
     <row r="37">
@@ -7062,55 +7062,55 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>309.4788530832886</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="C37" t="n">
-        <v>309.4788530832886</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="D37" t="n">
-        <v>289.7452994918185</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="E37" t="n">
-        <v>289.7452994918185</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="F37" t="n">
-        <v>289.7452994918185</v>
+        <v>330.8059241308429</v>
       </c>
       <c r="G37" t="n">
-        <v>310.8560555426382</v>
+        <v>351.9166801816626</v>
       </c>
       <c r="H37" t="n">
-        <v>350.95062234138</v>
+        <v>392.0112469804044</v>
       </c>
       <c r="I37" t="n">
-        <v>450.3756927528727</v>
+        <v>491.4363173918971</v>
       </c>
       <c r="J37" t="n">
-        <v>704.547677995488</v>
+        <v>745.6083026345125</v>
       </c>
       <c r="K37" t="n">
-        <v>724.5643873421925</v>
+        <v>765.625011981217</v>
       </c>
       <c r="L37" t="n">
-        <v>620.6698796815776</v>
+        <v>765.625011981217</v>
       </c>
       <c r="M37" t="n">
-        <v>421.7138224609195</v>
+        <v>765.625011981217</v>
       </c>
       <c r="N37" t="n">
-        <v>421.7138224609195</v>
+        <v>742.6295006763512</v>
       </c>
       <c r="O37" t="n">
-        <v>421.7138224609195</v>
+        <v>416.923466418694</v>
       </c>
       <c r="P37" t="n">
-        <v>421.7138224609195</v>
+        <v>36.16</v>
       </c>
       <c r="Q37" t="n">
-        <v>421.7138224609195</v>
+        <v>36.16</v>
       </c>
       <c r="R37" t="n">
-        <v>127.0312412961448</v>
+        <v>36.16</v>
       </c>
       <c r="S37" t="n">
         <v>36.16</v>
@@ -7141,19 +7141,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>809.4520555368546</v>
+        <v>920.6193217317157</v>
       </c>
       <c r="C38" t="n">
         <v>735.2914649206107</v>
       </c>
       <c r="D38" t="n">
-        <v>589.4943379106613</v>
+        <v>589.4943379106614</v>
       </c>
       <c r="E38" t="n">
-        <v>449.7334393178647</v>
+        <v>449.7334393178648</v>
       </c>
       <c r="F38" t="n">
-        <v>309.4408850673477</v>
+        <v>309.4408850673478</v>
       </c>
       <c r="G38" t="n">
         <v>171.1204085173441</v>
@@ -7165,25 +7165,25 @@
         <v>36.16</v>
       </c>
       <c r="J38" t="n">
-        <v>483.64</v>
+        <v>483.6400000000014</v>
       </c>
       <c r="K38" t="n">
-        <v>586.9166607035177</v>
+        <v>586.9166607035189</v>
       </c>
       <c r="L38" t="n">
-        <v>715.0404906532664</v>
+        <v>715.0404906532676</v>
       </c>
       <c r="M38" t="n">
-        <v>1162.520490653266</v>
+        <v>715.0404906532676</v>
       </c>
       <c r="N38" t="n">
-        <v>1176.801486248274</v>
+        <v>1162.520490653269</v>
       </c>
       <c r="O38" t="n">
-        <v>1244.052026827209</v>
+        <v>1229.771031232204</v>
       </c>
       <c r="P38" t="n">
-        <v>1360.52</v>
+        <v>1677.251031232205</v>
       </c>
       <c r="Q38" t="n">
         <v>1808</v>
@@ -7192,25 +7192,25 @@
         <v>1808</v>
       </c>
       <c r="S38" t="n">
-        <v>1595.717042826952</v>
+        <v>1808</v>
       </c>
       <c r="T38" t="n">
-        <v>1275.428566282694</v>
+        <v>1808</v>
       </c>
       <c r="U38" t="n">
-        <v>1275.428566282694</v>
+        <v>1808</v>
       </c>
       <c r="V38" t="n">
-        <v>1275.428566282694</v>
+        <v>1808</v>
       </c>
       <c r="W38" t="n">
-        <v>1275.428566282694</v>
+        <v>1716.173442033785</v>
       </c>
       <c r="X38" t="n">
-        <v>1275.428566282694</v>
+        <v>1386.595832477555</v>
       </c>
       <c r="Y38" t="n">
-        <v>1027.633179734405</v>
+        <v>1138.800445929266</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>411.8214757262247</v>
+        <v>429.3682977461393</v>
       </c>
       <c r="C39" t="n">
-        <v>315.760958104488</v>
+        <v>333.3077801244026</v>
       </c>
       <c r="D39" t="n">
-        <v>232.9956178037783</v>
+        <v>250.5424398236929</v>
       </c>
       <c r="E39" t="n">
-        <v>232.9956178037783</v>
+        <v>173.0958769732761</v>
       </c>
       <c r="F39" t="n">
-        <v>158.615575038246</v>
+        <v>98.71583420774388</v>
       </c>
       <c r="G39" t="n">
-        <v>98.71583420774385</v>
+        <v>98.71583420774388</v>
       </c>
       <c r="H39" t="n">
         <v>36.16</v>
       </c>
       <c r="I39" t="n">
-        <v>37.70035963146432</v>
+        <v>36.16</v>
       </c>
       <c r="J39" t="n">
-        <v>202.6985813161972</v>
+        <v>201.1582216847329</v>
       </c>
       <c r="K39" t="n">
-        <v>462.038202316241</v>
+        <v>460.4978426847767</v>
       </c>
       <c r="L39" t="n">
-        <v>827.7096997604978</v>
+        <v>826.1693401290335</v>
       </c>
       <c r="M39" t="n">
-        <v>1023.858441503357</v>
+        <v>1022.318081871893</v>
       </c>
       <c r="N39" t="n">
-        <v>1270.120103846774</v>
+        <v>1268.57974421531</v>
       </c>
       <c r="O39" t="n">
-        <v>1612.518443455021</v>
+        <v>1610.978083823557</v>
       </c>
       <c r="P39" t="n">
-        <v>1808</v>
+        <v>1806.459640368535</v>
       </c>
       <c r="Q39" t="n">
         <v>1808</v>
       </c>
       <c r="R39" t="n">
-        <v>1608.668684927291</v>
+        <v>1551.40386398902</v>
       </c>
       <c r="S39" t="n">
-        <v>1414.311490375654</v>
+        <v>1431.858312395569</v>
       </c>
       <c r="T39" t="n">
-        <v>1275.33257753921</v>
+        <v>1292.879399559125</v>
       </c>
       <c r="U39" t="n">
-        <v>1139.795717099151</v>
+        <v>1157.342539119066</v>
       </c>
       <c r="V39" t="n">
-        <v>989.7849421582216</v>
+        <v>1007.331764178136</v>
       </c>
       <c r="W39" t="n">
-        <v>821.7312624513241</v>
+        <v>839.2780844712388</v>
       </c>
       <c r="X39" t="n">
-        <v>666.3143539206296</v>
+        <v>683.8611759405443</v>
       </c>
       <c r="Y39" t="n">
-        <v>531.5755733487767</v>
+        <v>549.1223953686914</v>
       </c>
     </row>
     <row r="40">
@@ -7302,52 +7302,52 @@
         <v>287.7966784878721</v>
       </c>
       <c r="C40" t="n">
-        <v>281.0035000555038</v>
+        <v>287.7966784878721</v>
       </c>
       <c r="D40" t="n">
-        <v>261.2699464640336</v>
+        <v>287.7966784878721</v>
       </c>
       <c r="E40" t="n">
-        <v>261.2699464640336</v>
+        <v>287.7966784878721</v>
       </c>
       <c r="F40" t="n">
-        <v>261.2699464640336</v>
+        <v>287.7966784878721</v>
       </c>
       <c r="G40" t="n">
-        <v>282.3807025148533</v>
+        <v>308.9074345386918</v>
       </c>
       <c r="H40" t="n">
-        <v>322.4752693135951</v>
+        <v>349.0020013374336</v>
       </c>
       <c r="I40" t="n">
-        <v>421.9003397250879</v>
+        <v>448.4270717489264</v>
       </c>
       <c r="J40" t="n">
-        <v>676.0723249677031</v>
+        <v>702.5990569915416</v>
       </c>
       <c r="K40" t="n">
-        <v>696.0890343144076</v>
+        <v>722.6157663382461</v>
       </c>
       <c r="L40" t="n">
-        <v>592.1945266537928</v>
+        <v>618.7212586776312</v>
       </c>
       <c r="M40" t="n">
-        <v>592.1945266537928</v>
+        <v>618.7212586776312</v>
       </c>
       <c r="N40" t="n">
-        <v>592.1945266537928</v>
+        <v>618.7212586776312</v>
       </c>
       <c r="O40" t="n">
-        <v>592.1945266537928</v>
+        <v>618.7212586776312</v>
       </c>
       <c r="P40" t="n">
-        <v>469.5289559854526</v>
+        <v>618.7212586776312</v>
       </c>
       <c r="Q40" t="n">
-        <v>36.16</v>
+        <v>575.5781167200596</v>
       </c>
       <c r="R40" t="n">
-        <v>36.16</v>
+        <v>127.0312412961448</v>
       </c>
       <c r="S40" t="n">
         <v>36.16</v>
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>504.7850639419828</v>
+        <v>100.1052879389586</v>
       </c>
       <c r="C41" t="n">
-        <v>103.2955909692617</v>
+        <v>100.1052879389586</v>
       </c>
       <c r="D41" t="n">
-        <v>103.2955909692617</v>
+        <v>100.1052879389586</v>
       </c>
       <c r="E41" t="n">
-        <v>103.2955909692617</v>
+        <v>100.1052879389586</v>
       </c>
       <c r="F41" t="n">
-        <v>103.2955909692617</v>
+        <v>100.1052879389586</v>
       </c>
       <c r="G41" t="n">
-        <v>103.2955909692617</v>
+        <v>100.1052879389586</v>
       </c>
       <c r="H41" t="n">
-        <v>103.2955909692617</v>
+        <v>100.1052879389586</v>
       </c>
       <c r="I41" t="n">
-        <v>36.16</v>
+        <v>36</v>
       </c>
       <c r="J41" t="n">
-        <v>483.64</v>
+        <v>481.5000000000015</v>
       </c>
       <c r="K41" t="n">
-        <v>586.9166607035177</v>
+        <v>584.7766607035192</v>
       </c>
       <c r="L41" t="n">
-        <v>715.0404906532664</v>
+        <v>712.9004906532679</v>
       </c>
       <c r="M41" t="n">
-        <v>1162.520490653266</v>
+        <v>712.9004906532679</v>
       </c>
       <c r="N41" t="n">
-        <v>1176.801486248274</v>
+        <v>712.9004906532679</v>
       </c>
       <c r="O41" t="n">
-        <v>1244.052026827209</v>
+        <v>908.9999999999972</v>
       </c>
       <c r="P41" t="n">
-        <v>1360.52</v>
+        <v>1354.499999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>1808</v>
+        <v>1800</v>
       </c>
       <c r="R41" t="n">
-        <v>1659.148524608748</v>
+        <v>1654.178827639051</v>
       </c>
       <c r="S41" t="n">
-        <v>1230.703951274083</v>
+        <v>1463.741651575333</v>
       </c>
       <c r="T41" t="n">
-        <v>1230.703951274083</v>
+        <v>1463.741651575333</v>
       </c>
       <c r="U41" t="n">
-        <v>961.3507205076488</v>
+        <v>1009.196197029875</v>
       </c>
       <c r="V41" t="n">
-        <v>961.3507205076488</v>
+        <v>1009.196197029875</v>
       </c>
       <c r="W41" t="n">
-        <v>961.3507205076488</v>
+        <v>554.6507424844168</v>
       </c>
       <c r="X41" t="n">
-        <v>961.3507205076488</v>
+        <v>554.6507424844168</v>
       </c>
       <c r="Y41" t="n">
-        <v>504.7850639419828</v>
+        <v>100.1052879389586</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>297.6850347747348</v>
+        <v>311.687147339057</v>
       </c>
       <c r="C42" t="n">
-        <v>297.6850347747348</v>
+        <v>311.687147339057</v>
       </c>
       <c r="D42" t="n">
-        <v>297.6850347747348</v>
+        <v>311.687147339057</v>
       </c>
       <c r="E42" t="n">
-        <v>36.16</v>
+        <v>311.687147339057</v>
       </c>
       <c r="F42" t="n">
-        <v>36.16</v>
+        <v>311.687147339057</v>
       </c>
       <c r="G42" t="n">
-        <v>36.16</v>
+        <v>311.687147339057</v>
       </c>
       <c r="H42" t="n">
-        <v>36.16</v>
+        <v>36</v>
       </c>
       <c r="I42" t="n">
-        <v>36.16</v>
+        <v>36</v>
       </c>
       <c r="J42" t="n">
-        <v>201.1582216847329</v>
+        <v>200.9982216847329</v>
       </c>
       <c r="K42" t="n">
-        <v>462.038202316241</v>
+        <v>460.3378426847767</v>
       </c>
       <c r="L42" t="n">
-        <v>827.7096997604978</v>
+        <v>826.0093401290335</v>
       </c>
       <c r="M42" t="n">
-        <v>1023.858441503357</v>
+        <v>1022.158081871893</v>
       </c>
       <c r="N42" t="n">
-        <v>1270.120103846774</v>
+        <v>1268.41974421531</v>
       </c>
       <c r="O42" t="n">
-        <v>1612.518443455021</v>
+        <v>1610.818083823557</v>
       </c>
       <c r="P42" t="n">
-        <v>1808</v>
+        <v>1800</v>
       </c>
       <c r="Q42" t="n">
-        <v>1742.274956169327</v>
+        <v>1800</v>
       </c>
       <c r="R42" t="n">
-        <v>1742.274956169327</v>
+        <v>1345.45454545454</v>
       </c>
       <c r="S42" t="n">
-        <v>1742.274956169327</v>
+        <v>1043.377457073307</v>
       </c>
       <c r="T42" t="n">
-        <v>1387.134427171266</v>
+        <v>1043.377457073307</v>
       </c>
       <c r="U42" t="n">
-        <v>1035.435950569591</v>
+        <v>1043.377457073307</v>
       </c>
       <c r="V42" t="n">
-        <v>669.2635594670455</v>
+        <v>680.2353690010646</v>
       </c>
       <c r="W42" t="n">
-        <v>669.2635594670455</v>
+        <v>680.2353690010646</v>
       </c>
       <c r="X42" t="n">
-        <v>297.6850347747348</v>
+        <v>311.687147339057</v>
       </c>
       <c r="Y42" t="n">
-        <v>297.6850347747348</v>
+        <v>311.687147339057</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>78.47198524261526</v>
+        <v>36</v>
       </c>
       <c r="C43" t="n">
-        <v>36.16</v>
+        <v>36</v>
       </c>
       <c r="D43" t="n">
-        <v>36.16</v>
+        <v>36</v>
       </c>
       <c r="E43" t="n">
-        <v>36.16</v>
+        <v>36</v>
       </c>
       <c r="F43" t="n">
-        <v>36.16</v>
+        <v>36</v>
       </c>
       <c r="G43" t="n">
-        <v>36.16</v>
+        <v>36</v>
       </c>
       <c r="H43" t="n">
-        <v>36.16</v>
+        <v>36</v>
       </c>
       <c r="I43" t="n">
-        <v>36.16</v>
+        <v>36</v>
       </c>
       <c r="J43" t="n">
-        <v>78.47198524261526</v>
+        <v>81.28198524261525</v>
       </c>
       <c r="K43" t="n">
-        <v>78.47198524261526</v>
+        <v>81.28198524261525</v>
       </c>
       <c r="L43" t="n">
-        <v>78.47198524261526</v>
+        <v>81.28198524261525</v>
       </c>
       <c r="M43" t="n">
-        <v>78.47198524261526</v>
+        <v>81.28198524261525</v>
       </c>
       <c r="N43" t="n">
-        <v>78.47198524261526</v>
+        <v>81.28198524261525</v>
       </c>
       <c r="O43" t="n">
-        <v>78.47198524261526</v>
+        <v>81.28198524261525</v>
       </c>
       <c r="P43" t="n">
-        <v>78.47198524261526</v>
+        <v>81.28198524261525</v>
       </c>
       <c r="Q43" t="n">
-        <v>78.47198524261526</v>
+        <v>81.28198524261525</v>
       </c>
       <c r="R43" t="n">
-        <v>78.47198524261526</v>
+        <v>81.28198524261525</v>
       </c>
       <c r="S43" t="n">
-        <v>78.47198524261526</v>
+        <v>81.28198524261525</v>
       </c>
       <c r="T43" t="n">
-        <v>78.47198524261526</v>
+        <v>36</v>
       </c>
       <c r="U43" t="n">
-        <v>78.47198524261526</v>
+        <v>36</v>
       </c>
       <c r="V43" t="n">
-        <v>78.47198524261526</v>
+        <v>36</v>
       </c>
       <c r="W43" t="n">
-        <v>78.47198524261526</v>
+        <v>36</v>
       </c>
       <c r="X43" t="n">
-        <v>78.47198524261526</v>
+        <v>36</v>
       </c>
       <c r="Y43" t="n">
-        <v>78.47198524261526</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
@@ -7615,19 +7615,19 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>974.1218813979015</v>
+        <v>607.6553669722858</v>
       </c>
       <c r="C44" t="n">
-        <v>974.1218813979015</v>
+        <v>154.6507424844132</v>
       </c>
       <c r="D44" t="n">
-        <v>560.6479867111846</v>
+        <v>154.6507424844132</v>
       </c>
       <c r="E44" t="n">
-        <v>560.6479867111846</v>
+        <v>154.6507424844132</v>
       </c>
       <c r="F44" t="n">
-        <v>560.6479867111846</v>
+        <v>154.6507424844132</v>
       </c>
       <c r="G44" t="n">
         <v>154.6507424844132</v>
@@ -7651,40 +7651,40 @@
         <v>747.1168694455013</v>
       </c>
       <c r="N44" t="n">
-        <v>1192.616869445501</v>
+        <v>1170.781486248274</v>
       </c>
       <c r="O44" t="n">
-        <v>1259.867410024436</v>
+        <v>1238.032026827209</v>
       </c>
       <c r="P44" t="n">
-        <v>1376.335383197227</v>
+        <v>1354.5</v>
       </c>
       <c r="Q44" t="n">
         <v>1800</v>
       </c>
       <c r="R44" t="n">
-        <v>1599.633373093596</v>
+        <v>1800</v>
       </c>
       <c r="S44" t="n">
-        <v>1599.633373093596</v>
+        <v>1345.454545454542</v>
       </c>
       <c r="T44" t="n">
-        <v>1145.087918548142</v>
+        <v>1345.454545454542</v>
       </c>
       <c r="U44" t="n">
-        <v>1145.087918548142</v>
+        <v>1345.454545454542</v>
       </c>
       <c r="V44" t="n">
-        <v>1145.087918548142</v>
+        <v>1345.454545454542</v>
       </c>
       <c r="W44" t="n">
-        <v>974.1218813979015</v>
+        <v>1345.454545454542</v>
       </c>
       <c r="X44" t="n">
-        <v>974.1218813979015</v>
+        <v>1345.454545454542</v>
       </c>
       <c r="Y44" t="n">
-        <v>974.1218813979015</v>
+        <v>1062.200821517743</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>363.5765085072699</v>
+        <v>239.0493320419568</v>
       </c>
       <c r="C45" t="n">
-        <v>363.5765085072699</v>
+        <v>239.0493320419568</v>
       </c>
       <c r="D45" t="n">
-        <v>363.5765085072699</v>
+        <v>239.0493320419568</v>
       </c>
       <c r="E45" t="n">
-        <v>363.5765085072699</v>
+        <v>239.0493320419568</v>
       </c>
       <c r="F45" t="n">
-        <v>363.5765085072699</v>
+        <v>239.0493320419568</v>
       </c>
       <c r="G45" t="n">
-        <v>36</v>
+        <v>239.0493320419568</v>
       </c>
       <c r="H45" t="n">
-        <v>36</v>
+        <v>239.0493320419568</v>
       </c>
       <c r="I45" t="n">
         <v>36</v>
@@ -7721,13 +7721,13 @@
         <v>200.9982216847329</v>
       </c>
       <c r="K45" t="n">
-        <v>454.038202316241</v>
+        <v>460.3378426847767</v>
       </c>
       <c r="L45" t="n">
-        <v>819.7096997604978</v>
+        <v>826.0093401290335</v>
       </c>
       <c r="M45" t="n">
-        <v>1015.858441503357</v>
+        <v>1022.158081871893</v>
       </c>
       <c r="N45" t="n">
         <v>1262.120103846774</v>
@@ -7739,31 +7739,31 @@
         <v>1800</v>
       </c>
       <c r="Q45" t="n">
-        <v>1800</v>
+        <v>1682.759804654175</v>
       </c>
       <c r="R45" t="n">
-        <v>1800</v>
+        <v>1682.759804654175</v>
       </c>
       <c r="S45" t="n">
-        <v>1800</v>
+        <v>1500.289003881705</v>
       </c>
       <c r="T45" t="n">
-        <v>1800</v>
+        <v>1500.289003881705</v>
       </c>
       <c r="U45" t="n">
-        <v>1396.786371883173</v>
+        <v>1500.289003881705</v>
       </c>
       <c r="V45" t="n">
-        <v>979.0988292654761</v>
+        <v>1500.289003881705</v>
       </c>
       <c r="W45" t="n">
-        <v>979.0988292654761</v>
+        <v>1064.55855649804</v>
       </c>
       <c r="X45" t="n">
-        <v>751.0073738065897</v>
+        <v>641.4648802905774</v>
       </c>
       <c r="Y45" t="n">
-        <v>751.0073738065897</v>
+        <v>239.0493320419568</v>
       </c>
     </row>
     <row r="46">
@@ -7967,13 +7967,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>370.6801407035176</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>345.5819899497487</v>
+        <v>40.12587555835679</v>
       </c>
       <c r="M2" t="n">
-        <v>400.2596552805082</v>
+        <v>875.2596552805082</v>
       </c>
       <c r="N2" t="n">
         <v>805.9163751552624</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>358.1248010918721</v>
+        <v>559.2610561867818</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8207,7 +8207,7 @@
         <v>370.6801407035176</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>134.9932348548393</v>
       </c>
       <c r="M5" t="n">
         <v>875.2596552805082</v>
@@ -8222,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>228.7067910416209</v>
+        <v>93.71355618678184</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,16 +8441,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>204.7866490224515</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>345.5819899497487</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>875.2596552805082</v>
       </c>
       <c r="N8" t="n">
-        <v>330.9163751552624</v>
+        <v>415.7375141274626</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.71355618678184</v>
+        <v>559.2610561867818</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>370.6801407035176</v>
+        <v>370.6801407035175</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>345.5819899497487</v>
       </c>
       <c r="M11" t="n">
-        <v>551.2087343572709</v>
+        <v>875.2596552805082</v>
       </c>
       <c r="N11" t="n">
-        <v>330.9163751552624</v>
+        <v>566.5882008684332</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>559.2610561867818</v>
+        <v>84.26105618678189</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8924,7 +8924,7 @@
         <v>875.2596552805082</v>
       </c>
       <c r="N14" t="n">
-        <v>377.545594935543</v>
+        <v>805.9163751552624</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>559.2610561867818</v>
+        <v>130.8902759670625</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>370.6801407035175</v>
+        <v>372.6801407035176</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>875.2596552805082</v>
+        <v>555.1279262764631</v>
       </c>
       <c r="N17" t="n">
-        <v>805.9163751552624</v>
+        <v>330.9163751552624</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>190.5148718497017</v>
+        <v>561.2610561867818</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,10 +9386,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>372.6801407035175</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -9398,16 +9398,16 @@
         <v>877.2596552805082</v>
       </c>
       <c r="N20" t="n">
-        <v>381.4647868547348</v>
+        <v>330.9163751552624</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>409.0701610313789</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>561.2610561867818</v>
+        <v>260.3639027375146</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,10 +9623,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>372.6801407035175</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9635,7 +9635,7 @@
         <v>877.2596552805082</v>
       </c>
       <c r="N23" t="n">
-        <v>381.4647868547348</v>
+        <v>439.089382737374</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>417.4380012199659</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>82.35508704438314</v>
       </c>
       <c r="M26" t="n">
-        <v>832.1229045762384</v>
+        <v>400.2596552805082</v>
       </c>
       <c r="N26" t="n">
-        <v>782.9163751552624</v>
+        <v>330.9163751552624</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>384.0701610313801</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>536.2610561867818</v>
+        <v>536.2610561867831</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>347.6801407035176</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>322.5819899497487</v>
       </c>
       <c r="M29" t="n">
-        <v>400.2596552805082</v>
+        <v>852.2596552805095</v>
       </c>
       <c r="N29" t="n">
-        <v>782.9163751552624</v>
+        <v>782.9163751552636</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>297.8621748292458</v>
+        <v>193.5423155327609</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,19 +10334,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>417.4380012199647</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>347.6801407035176</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>852.2596552805082</v>
+        <v>852.2596552805096</v>
       </c>
       <c r="N32" t="n">
-        <v>330.9163751552624</v>
+        <v>762.7796244509898</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>203.0061635590296</v>
+        <v>536.2610561867832</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,16 +10574,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>347.6801407035176</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>852.2596552805082</v>
+        <v>852.2596552805096</v>
       </c>
       <c r="N35" t="n">
-        <v>762.7796244509925</v>
+        <v>415.0994837474722</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>536.2610561867818</v>
+        <v>536.2610561867832</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,7 +10808,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>417.4380012199647</v>
+        <v>417.4380012199661</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -10817,19 +10817,19 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>852.2596552805082</v>
+        <v>400.2596552805082</v>
       </c>
       <c r="N38" t="n">
-        <v>345.3416232310279</v>
+        <v>782.9163751552637</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>334.3555826537481</v>
       </c>
       <c r="Q38" t="n">
-        <v>536.2610561867818</v>
+        <v>216.3307216087966</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>417.4380012199647</v>
+        <v>415.4380012199662</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -11054,19 +11054,19 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>852.2596552805082</v>
+        <v>400.2596552805082</v>
       </c>
       <c r="N41" t="n">
-        <v>345.3416232310279</v>
+        <v>330.9163751552624</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>130.1504735028226</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>332.3555826537482</v>
       </c>
       <c r="Q41" t="n">
-        <v>536.2610561867818</v>
+        <v>534.2610561867833</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11142,7 +11142,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P42" t="n">
-        <v>219.1507118405495</v>
+        <v>212.7874387410187</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11294,7 +11294,7 @@
         <v>850.2596552805082</v>
       </c>
       <c r="N44" t="n">
-        <v>780.9163751552624</v>
+        <v>758.8604325318006</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>512.2051135633201</v>
+        <v>534.2610561867818</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11364,7 +11364,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
-        <v>289.5169677634825</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
         <v>388.0893364597981</v>
@@ -11373,7 +11373,7 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>485.4085271713503</v>
+        <v>479.0452540718193</v>
       </c>
       <c r="O45" t="n">
         <v>382.6817988009037</v>
@@ -22512,10 +22512,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>98.48973009952613</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -22572,16 +22572,16 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>229.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>41.40889620541361</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -22591,22 +22591,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.3007434221972</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -22639,7 +22639,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>95.7557111487493</v>
+        <v>45.03017465086985</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -22673,19 +22673,19 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>231.4559167985597</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>244.676003989071</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -22703,19 +22703,19 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>462.9664966484515</v>
+        <v>62.96649664845154</v>
       </c>
       <c r="N4" t="n">
         <v>114.8911080585701</v>
       </c>
       <c r="O4" t="n">
-        <v>188.4489739150805</v>
+        <v>588.4489739150805</v>
       </c>
       <c r="P4" t="n">
         <v>242.955831754507</v>
       </c>
       <c r="Q4" t="n">
-        <v>295.035266425598</v>
+        <v>695.035266425598</v>
       </c>
       <c r="R4" t="n">
         <v>710.0614066696756</v>
@@ -22736,10 +22736,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -22755,7 +22755,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -22764,13 +22764,13 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.93727178450365</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>399.6108044321707</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>118.464235059569</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -22800,7 +22800,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>172.1936792031823</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -22809,7 +22809,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>98.97349053730974</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -22828,13 +22828,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -22843,10 +22843,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.3007434221972</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>327.9302758656664</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -22882,22 +22882,22 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>403.5891237080799</v>
       </c>
       <c r="U6" t="n">
-        <v>400.1814918356584</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>414.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>419.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>162.3619093651728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22922,7 +22922,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>244.676003989071</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>462.9664966484515</v>
+        <v>62.96649664845154</v>
       </c>
       <c r="N7" t="n">
         <v>114.8911080585701</v>
@@ -22949,7 +22949,7 @@
         <v>188.4489739150805</v>
       </c>
       <c r="P7" t="n">
-        <v>642.955831754507</v>
+        <v>242.955831754507</v>
       </c>
       <c r="Q7" t="n">
         <v>295.035266425598</v>
@@ -22970,7 +22970,7 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>481.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -23065,10 +23065,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -23134,7 +23134,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -23144,22 +23144,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>244.676003989071</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -23171,13 +23171,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>245.7811016699955</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>368.8555625840087</v>
       </c>
       <c r="M10" t="n">
-        <v>66.32705841572277</v>
+        <v>462.9664966484515</v>
       </c>
       <c r="N10" t="n">
         <v>514.8911080585701</v>
@@ -23186,16 +23186,16 @@
         <v>588.4489739150805</v>
       </c>
       <c r="P10" t="n">
-        <v>242.955831754507</v>
+        <v>642.955831754507</v>
       </c>
       <c r="Q10" t="n">
-        <v>295.035266425598</v>
+        <v>695.035266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>310.0614066696756</v>
+        <v>710.0614066696756</v>
       </c>
       <c r="S10" t="n">
-        <v>355.9625288831833</v>
+        <v>118.8912056865159</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -23213,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -23223,7 +23223,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>186.6887986269533</v>
+        <v>212.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>180.4745782429939</v>
@@ -23235,10 +23235,10 @@
         <v>135.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>135.8896287080119</v>
+        <v>102.4263552921706</v>
       </c>
       <c r="G11" t="n">
-        <v>133.9372717845037</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>130.6108044321706</v>
@@ -23274,13 +23274,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>207.1601276013179</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>314.0855917788151</v>
       </c>
       <c r="U11" t="n">
-        <v>380.1556885084096</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -23390,7 +23390,7 @@
         <v>16.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>11.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>5.382855967741932</v>
@@ -23417,19 +23417,19 @@
         <v>193.9664966484515</v>
       </c>
       <c r="N13" t="n">
-        <v>40.80703459948674</v>
+        <v>245.8911080585701</v>
       </c>
       <c r="O13" t="n">
         <v>319.4489739150805</v>
       </c>
       <c r="P13" t="n">
-        <v>373.955831754507</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>426.035266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>162.3873102829179</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -23450,7 +23450,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>18.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -23460,25 +23460,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>106.9188993922624</v>
+        <v>212.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>180.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>141.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>135.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>135.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>133.9372717845037</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>130.6108044321706</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,25 +23511,25 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>207.1601276013179</v>
+        <v>111.5277414969818</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>380.1556885084096</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>360.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>369.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>242.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -23648,10 +23648,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>99.85556258400868</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>135.7979404566344</v>
+        <v>193.9664966484515</v>
       </c>
       <c r="N16" t="n">
         <v>245.8911080585701</v>
@@ -23660,10 +23660,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>373.955831754507</v>
       </c>
       <c r="Q16" t="n">
-        <v>426.035266425598</v>
+        <v>93.76644106328263</v>
       </c>
       <c r="R16" t="n">
         <v>441.0614066696756</v>
@@ -23697,22 +23697,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>212.9993129555745</v>
+        <v>211.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>180.4745782429939</v>
+        <v>179.4745782429939</v>
       </c>
       <c r="D17" t="n">
-        <v>141.3391557398498</v>
+        <v>140.3391557398498</v>
       </c>
       <c r="E17" t="n">
-        <v>135.3632896068686</v>
+        <v>134.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>135.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>133.9372717845037</v>
+        <v>132.9372717845037</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23748,25 +23748,25 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>206.1601276013179</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>313.0855917788151</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>84.33828793983776</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>369.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>115.0825026310113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -23855,19 +23855,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18.11380033707866</v>
+        <v>17.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2.725246648044674</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>15.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>11.98090483695654</v>
+        <v>10.98090483695654</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>4.382855967741932</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -23885,28 +23885,28 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>95.9169535952566</v>
+        <v>98.85556258400868</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>192.9664966484515</v>
       </c>
       <c r="N19" t="n">
-        <v>245.8911080585701</v>
+        <v>244.8911080585701</v>
       </c>
       <c r="O19" t="n">
-        <v>319.4489739150805</v>
+        <v>318.4489739150805</v>
       </c>
       <c r="P19" t="n">
-        <v>373.955831754507</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>426.035266425598</v>
+        <v>36.61673631870053</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>440.0614066696756</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>85.96252888318331</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23924,7 +23924,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>18.46535284946236</v>
+        <v>17.46535284946236</v>
       </c>
     </row>
     <row r="20">
@@ -23937,7 +23937,7 @@
         <v>211.9993129555745</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>179.4745782429939</v>
       </c>
       <c r="D20" t="n">
         <v>140.3391557398498</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>206.1601276013179</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -23994,16 +23994,16 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>359.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>158.7071282559582</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>132.9234465784702</v>
       </c>
     </row>
     <row r="21">
@@ -24125,22 +24125,22 @@
         <v>98.85556258400868</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>192.9664966484515</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>244.8911080585701</v>
       </c>
       <c r="O22" t="n">
-        <v>318.4489739150805</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>66.90442744958654</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>425.035266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>440.0614066696756</v>
+        <v>370.0918504778587</v>
       </c>
       <c r="S22" t="n">
         <v>85.96252888318331</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>17.46535284946236</v>
       </c>
     </row>
     <row r="23">
@@ -24174,22 +24174,22 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>179.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>140.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>134.3632896068686</v>
       </c>
       <c r="F23" t="n">
         <v>134.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>132.9372717845037</v>
       </c>
       <c r="H23" t="n">
-        <v>129.6108044321707</v>
+        <v>129.6108044321706</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24222,19 +24222,19 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>206.1601276013179</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>313.0855917788151</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>61.90716722365164</v>
+        <v>95.19004013887394</v>
       </c>
       <c r="W23" t="n">
-        <v>368.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>322.2818334606677</v>
@@ -24371,16 +24371,16 @@
         <v>318.4489739150805</v>
       </c>
       <c r="P25" t="n">
-        <v>36.61673631870053</v>
+        <v>372.955831754507</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>440.0614066696756</v>
+        <v>189.6848401170525</v>
       </c>
       <c r="S25" t="n">
-        <v>85.96252888318332</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24411,10 +24411,10 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>237.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>195.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -24423,10 +24423,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>187.9372717845037</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>184.6108044321707</v>
+        <v>187.6108044321707</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,22 +24459,22 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>107.4562457785209</v>
+        <v>264.1601276013179</v>
       </c>
       <c r="T26" t="n">
-        <v>368.0855917788151</v>
+        <v>371.0855917788151</v>
       </c>
       <c r="U26" t="n">
-        <v>434.1556885084096</v>
+        <v>437.1556885084096</v>
       </c>
       <c r="V26" t="n">
-        <v>414.8510241668239</v>
+        <v>7.575515644438838</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>426.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>377.2818334606677</v>
+        <v>380.2818334606677</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -24490,7 +24490,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>146.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -24499,13 +24499,13 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>124.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>113.3007434221972</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>115.9302758656664</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24535,10 +24535,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>305.0301746508699</v>
+        <v>247.3464851469883</v>
       </c>
       <c r="S27" t="n">
-        <v>117.7352010711479</v>
+        <v>246.4136226061207</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -24550,10 +24550,10 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>220.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>204.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -24566,22 +24566,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>72.11380033707866</v>
+        <v>75.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>57.72524664804467</v>
+        <v>60.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>70.53621805555548</v>
+        <v>73.53621805555548</v>
       </c>
       <c r="E28" t="n">
-        <v>65.98090483695654</v>
+        <v>68.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>59.38285596774193</v>
+        <v>62.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>29.67600398907101</v>
+        <v>32.67600398907101</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -24593,31 +24593,31 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>30.78110166999551</v>
+        <v>33.78110166999551</v>
       </c>
       <c r="L28" t="n">
-        <v>153.8555625840087</v>
+        <v>156.8555625840087</v>
       </c>
       <c r="M28" t="n">
-        <v>247.9664966484515</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>299.8911080585701</v>
+        <v>261.6229943266907</v>
       </c>
       <c r="O28" t="n">
-        <v>60.51286353474956</v>
+        <v>376.4489739150805</v>
       </c>
       <c r="P28" t="n">
-        <v>427.955831754507</v>
+        <v>430.955831754507</v>
       </c>
       <c r="Q28" t="n">
-        <v>480.035266425598</v>
+        <v>483.035266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>495.0614066696756</v>
+        <v>498.0614066696756</v>
       </c>
       <c r="S28" t="n">
-        <v>140.9625288831833</v>
+        <v>143.9625288831833</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24632,10 +24632,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>32.44364543010755</v>
+        <v>35.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>72.46535284946236</v>
+        <v>75.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -24645,19 +24645,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25.82293254595663</v>
+        <v>215.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>183.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>144.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>138.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>136.9372717845037</v>
@@ -24702,19 +24702,19 @@
         <v>317.0855917788151</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>383.1556885084096</v>
       </c>
       <c r="V29" t="n">
         <v>363.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>138.6887264556345</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>245.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24775,7 +24775,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>133.3642699508015</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>133.3642699508012</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -24803,19 +24803,19 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>21.11380033707866</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>6.725246648044674</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>19.53621805555548</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>14.98090483695654</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>8.382855967741932</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -24833,16 +24833,16 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>102.8555625840087</v>
       </c>
       <c r="M31" t="n">
         <v>196.9664966484515</v>
       </c>
       <c r="N31" t="n">
-        <v>248.8911080585701</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>322.4489739150805</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>376.955831754507</v>
@@ -24851,10 +24851,10 @@
         <v>429.035266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>293.2311267819215</v>
       </c>
       <c r="S31" t="n">
-        <v>6.913514970302586</v>
+        <v>89.96252888318331</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24872,7 +24872,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>21.46535284946236</v>
       </c>
     </row>
     <row r="32">
@@ -24888,16 +24888,16 @@
         <v>183.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>144.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>138.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>138.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>136.9372717845037</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -24933,25 +24933,25 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>210.1601276013179</v>
       </c>
       <c r="T32" t="n">
         <v>317.0855917788151</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>383.1556885084096</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>108.9050447781466</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>172.248625934841</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>245.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -24967,7 +24967,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>81.93768689770263</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -25009,7 +25009,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>133.3642699508014</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -25030,7 +25030,7 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>51.4265830530986</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -25040,13 +25040,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>21.11380033707866</v>
       </c>
       <c r="C34" t="n">
         <v>6.725246648044674</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>19.53621805555548</v>
       </c>
       <c r="E34" t="n">
         <v>14.98090483695654</v>
@@ -25079,19 +25079,19 @@
         <v>248.8911080585701</v>
       </c>
       <c r="O34" t="n">
-        <v>322.4489739150805</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>376.955831754507</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>429.035266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>191.5763296265031</v>
+        <v>134.3025476065347</v>
       </c>
       <c r="S34" t="n">
-        <v>89.96252888318331</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25125,19 +25125,19 @@
         <v>183.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>144.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>138.3632896068686</v>
       </c>
       <c r="F35" t="n">
-        <v>138.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>136.9372717845037</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>133.6108044321706</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -25170,22 +25170,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>210.1601276013179</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>8.6260138956641</v>
+        <v>317.0855917788151</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>129.195576922035</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>326.2818334606677</v>
       </c>
       <c r="Y35" t="n">
         <v>245.3174326828064</v>
@@ -25207,7 +25207,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>76.67209722191262</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -25249,7 +25249,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>56.69217272888847</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
@@ -25261,7 +25261,7 @@
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>133.3642699508012</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -25277,13 +25277,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>21.11380033707866</v>
       </c>
       <c r="C37" t="n">
         <v>6.725246648044674</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>19.53621805555548</v>
       </c>
       <c r="E37" t="n">
         <v>14.98090483695654</v>
@@ -25307,28 +25307,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>102.8555625840087</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>196.9664966484515</v>
       </c>
       <c r="N37" t="n">
-        <v>248.8911080585701</v>
+        <v>226.125551866753</v>
       </c>
       <c r="O37" t="n">
-        <v>322.4489739150805</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>376.955831754507</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>429.035266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>152.3256513165486</v>
+        <v>444.0614066696756</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>89.96252888318332</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25359,7 +25359,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>110.0555935329125</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -25407,10 +25407,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>210.1601276013179</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>317.0855917788151</v>
       </c>
       <c r="U38" t="n">
         <v>383.1556885084096</v>
@@ -25419,10 +25419,10 @@
         <v>363.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>372.3734759809475</v>
+        <v>281.4651835943947</v>
       </c>
       <c r="X38" t="n">
-        <v>326.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
         <v>0</v>
@@ -25444,13 +25444,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>76.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>59.30074342219717</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -25483,10 +25483,10 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>56.69217272888841</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>74.06352652860433</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
@@ -25517,10 +25517,10 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>6.725246648044674</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>19.53621805555548</v>
       </c>
       <c r="E40" t="n">
         <v>14.98090483695654</v>
@@ -25556,16 +25556,16 @@
         <v>322.4489739150805</v>
       </c>
       <c r="P40" t="n">
-        <v>255.5169167928503</v>
+        <v>376.955831754507</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>386.3235558876021</v>
       </c>
       <c r="R40" t="n">
-        <v>444.0614066696756</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>89.96252888318331</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>429.9993129555745</v>
+        <v>426.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>394.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>358.3391557398498</v>
+        <v>355.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>352.3632896068686</v>
+        <v>349.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>352.8896287080119</v>
+        <v>349.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>350.9372717845037</v>
+        <v>347.9372717845037</v>
       </c>
       <c r="H41" t="n">
-        <v>347.6108044321707</v>
+        <v>344.6108044321707</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,25 +25644,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>232.6273232982377</v>
       </c>
       <c r="T41" t="n">
-        <v>531.0855917788151</v>
+        <v>528.0855917788151</v>
       </c>
       <c r="U41" t="n">
-        <v>330.4959900496395</v>
+        <v>144.1556885084057</v>
       </c>
       <c r="V41" t="n">
-        <v>577.8510241668239</v>
+        <v>574.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>586.3734759809475</v>
+        <v>133.3734759809441</v>
       </c>
       <c r="X41" t="n">
-        <v>540.2818334606677</v>
+        <v>537.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.317432682797062</v>
+        <v>6.31743268280286</v>
       </c>
     </row>
     <row r="42">
@@ -25672,28 +25672,28 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>332.5565566463266</v>
+        <v>329.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>309.0999124455193</v>
+        <v>306.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>295.9376868977026</v>
+        <v>292.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>31.76231279492515</v>
+        <v>287.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>287.6362423378769</v>
+        <v>284.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>273.3007434221972</v>
+        <v>270.3007434221972</v>
       </c>
       <c r="H42" t="n">
-        <v>275.9302758656664</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>150.0188387215372</v>
+        <v>147.0188387215372</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -25717,31 +25717,31 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>62.06779339236638</v>
       </c>
       <c r="R42" t="n">
-        <v>468.0301746508699</v>
+        <v>15.03017465086498</v>
       </c>
       <c r="S42" t="n">
-        <v>406.4136226061207</v>
+        <v>104.3573051086997</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>348.5891237080799</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>345.1814918356584</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>380.3731429098285</v>
+        <v>377.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>347.3913927661343</v>
+        <v>344.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -25751,76 +25751,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>235.1138003370787</v>
+        <v>232.1138003370787</v>
       </c>
       <c r="C43" t="n">
-        <v>178.8363812578556</v>
+        <v>217.7252466480447</v>
       </c>
       <c r="D43" t="n">
-        <v>233.5362180555555</v>
+        <v>230.5362180555555</v>
       </c>
       <c r="E43" t="n">
-        <v>228.9809048369565</v>
+        <v>225.9809048369565</v>
       </c>
       <c r="F43" t="n">
-        <v>222.3828559677419</v>
+        <v>219.3828559677419</v>
       </c>
       <c r="G43" t="n">
-        <v>192.676003989071</v>
+        <v>189.676003989071</v>
       </c>
       <c r="H43" t="n">
-        <v>173.5004375770285</v>
+        <v>170.5004375770285</v>
       </c>
       <c r="I43" t="n">
-        <v>113.5706359479871</v>
+        <v>110.5706359479871</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>193.7811016699955</v>
+        <v>190.7811016699955</v>
       </c>
       <c r="L43" t="n">
-        <v>316.8555625840087</v>
+        <v>313.8555625840087</v>
       </c>
       <c r="M43" t="n">
-        <v>410.9664966484515</v>
+        <v>407.9664966484515</v>
       </c>
       <c r="N43" t="n">
-        <v>462.8911080585701</v>
+        <v>459.8911080585701</v>
       </c>
       <c r="O43" t="n">
-        <v>536.4489739150805</v>
+        <v>533.4489739150805</v>
       </c>
       <c r="P43" t="n">
-        <v>590.955831754507</v>
+        <v>587.955831754507</v>
       </c>
       <c r="Q43" t="n">
-        <v>643.035266425598</v>
+        <v>640.035266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>658.0614066696756</v>
+        <v>655.0614066696756</v>
       </c>
       <c r="S43" t="n">
-        <v>303.9625288831833</v>
+        <v>300.9625288831833</v>
       </c>
       <c r="T43" t="n">
-        <v>156.4527632275692</v>
+        <v>108.6235978373801</v>
       </c>
       <c r="U43" t="n">
-        <v>98.93832570068744</v>
+        <v>95.93832570068744</v>
       </c>
       <c r="V43" t="n">
-        <v>147.1703102162162</v>
+        <v>144.1703102162162</v>
       </c>
       <c r="W43" t="n">
-        <v>174.3728098387097</v>
+        <v>171.3728098387097</v>
       </c>
       <c r="X43" t="n">
-        <v>195.4436454301076</v>
+        <v>192.4436454301076</v>
       </c>
       <c r="Y43" t="n">
-        <v>235.4653528494624</v>
+        <v>232.4653528494624</v>
       </c>
     </row>
     <row r="44">
@@ -25830,13 +25830,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>480.9993129555745</v>
+        <v>30.99931295557201</v>
       </c>
       <c r="C44" t="n">
-        <v>448.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>409.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>403.3632896068686</v>
@@ -25845,7 +25845,7 @@
         <v>403.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>401.9372717845037</v>
       </c>
       <c r="H44" t="n">
         <v>398.6108044321707</v>
@@ -25878,13 +25878,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>198.3629606373397</v>
       </c>
       <c r="S44" t="n">
-        <v>475.1601276013179</v>
+        <v>25.16012760131446</v>
       </c>
       <c r="T44" t="n">
-        <v>132.0855917788151</v>
+        <v>582.0855917788151</v>
       </c>
       <c r="U44" t="n">
         <v>648.1556885084096</v>
@@ -25893,13 +25893,13 @@
         <v>628.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>468.1170992022097</v>
+        <v>637.3734759809475</v>
       </c>
       <c r="X44" t="n">
         <v>591.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>510.3174326828064</v>
+        <v>229.8962459853755</v>
       </c>
     </row>
     <row r="45">
@@ -25909,7 +25909,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>383.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>360.0999124455193</v>
@@ -25924,13 +25924,13 @@
         <v>338.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>324.3007434221972</v>
       </c>
       <c r="H45" t="n">
         <v>326.9302758656664</v>
       </c>
       <c r="I45" t="n">
-        <v>201.0188387215372</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25954,31 +25954,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>116.0677933923664</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>519.0301746508699</v>
       </c>
       <c r="S45" t="n">
-        <v>457.4136226061207</v>
+        <v>276.7675298413749</v>
       </c>
       <c r="T45" t="n">
         <v>402.5891237080799</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>399.1814918356584</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>413.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>431.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>193.0521985410901</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>398.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>971014.6924282878</v>
+        <v>971014.692428288</v>
       </c>
     </row>
     <row r="3">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3391529.469988036</v>
+        <v>3391529.469988037</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4196101.620357178</v>
+        <v>4196101.62035718</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5000673.77072632</v>
+        <v>5002658.953900707</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5807231.104269842</v>
+        <v>5808901.103605846</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6613473.253974978</v>
+        <v>6615143.253310982</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7315306.865197306</v>
+        <v>7311922.13843331</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8106962.063444156</v>
+        <v>8103577.336680162</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8898617.261691008</v>
+        <v>8895232.534927012</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9690272.459937857</v>
+        <v>9686887.733173862</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10481927.65818472</v>
+        <v>10478542.93142072</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10893930.50287354</v>
+        <v>10894998.75858145</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11209771.00775165</v>
+        <v>11211289.34868765</v>
       </c>
     </row>
   </sheetData>
@@ -26275,7 +26275,7 @@
         <v>1143378.780837107</v>
       </c>
       <c r="D2" t="n">
-        <v>1143378.780837106</v>
+        <v>1143378.780837107</v>
       </c>
       <c r="E2" t="n">
         <v>1137498.557418442</v>
@@ -26284,7 +26284,7 @@
         <v>1137498.557418442</v>
       </c>
       <c r="G2" t="n">
-        <v>1137498.557418442</v>
+        <v>1139859.590962442</v>
       </c>
       <c r="H2" t="n">
         <v>1139859.590962442</v>
@@ -26293,7 +26293,7 @@
         <v>1139859.590962442</v>
       </c>
       <c r="J2" t="n">
-        <v>997817.5785271521</v>
+        <v>990671.2416271515</v>
       </c>
       <c r="K2" t="n">
         <v>1119236.65959038</v>
@@ -26308,10 +26308,10 @@
         <v>1119236.65959038</v>
       </c>
       <c r="O2" t="n">
-        <v>582486.7804221117</v>
+        <v>589418.7037221115</v>
       </c>
       <c r="P2" t="n">
-        <v>447169.4549777237</v>
+        <v>447169.4549777236</v>
       </c>
     </row>
     <row r="3">
@@ -26336,25 +26336,25 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1504</v>
       </c>
       <c r="H3" t="n">
-        <v>1504</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>329600</v>
+        <v>327200</v>
       </c>
       <c r="K3" t="n">
-        <v>40800</v>
+        <v>43200</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="M3" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>548102.6727173403</v>
+        <v>551162.4224229963</v>
       </c>
       <c r="C4" t="n">
-        <v>546554.3588594097</v>
+        <v>549614.1085650658</v>
       </c>
       <c r="D4" t="n">
-        <v>545003.9446170919</v>
+        <v>548063.6943227479</v>
       </c>
       <c r="E4" t="n">
-        <v>538747.0315038303</v>
+        <v>541778.1218508939</v>
       </c>
       <c r="F4" t="n">
-        <v>537204.5846327126</v>
+        <v>540235.6749797761</v>
       </c>
       <c r="G4" t="n">
-        <v>535660.0092427835</v>
+        <v>539952.771499335</v>
       </c>
       <c r="H4" t="n">
-        <v>535365.1382690049</v>
+        <v>538402.171207218</v>
       </c>
       <c r="I4" t="n">
-        <v>533812.3733137125</v>
+        <v>536849.4062519256</v>
       </c>
       <c r="J4" t="n">
-        <v>455600.5828099435</v>
+        <v>454693.099431961</v>
       </c>
       <c r="K4" t="n">
-        <v>519871.46089542</v>
+        <v>522834.2114442637</v>
       </c>
       <c r="L4" t="n">
-        <v>518341.1428830695</v>
+        <v>521303.8934319132</v>
       </c>
       <c r="M4" t="n">
-        <v>516808.6376315783</v>
+        <v>519771.3881804221</v>
       </c>
       <c r="N4" t="n">
-        <v>515273.9288923686</v>
+        <v>518236.6794412123</v>
       </c>
       <c r="O4" t="n">
-        <v>229284.7085689683</v>
+        <v>235939.6677080049</v>
       </c>
       <c r="P4" t="n">
-        <v>157634.7557234491</v>
+        <v>160589.0202010947</v>
       </c>
     </row>
     <row r="5">
@@ -26440,7 +26440,7 @@
         <v>55941.761</v>
       </c>
       <c r="G5" t="n">
-        <v>55941.761</v>
+        <v>56147.43</v>
       </c>
       <c r="H5" t="n">
         <v>56147.43</v>
@@ -26449,7 +26449,7 @@
         <v>56147.43</v>
       </c>
       <c r="J5" t="n">
-        <v>50003.63499999999</v>
+        <v>49751.428</v>
       </c>
       <c r="K5" t="n">
         <v>54291.15399999999</v>
@@ -26464,7 +26464,7 @@
         <v>54291.15399999999</v>
       </c>
       <c r="O5" t="n">
-        <v>36300.388</v>
+        <v>36430.995</v>
       </c>
       <c r="P5" t="n">
         <v>31891.269</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>162221.3081197662</v>
+        <v>159161.5584141107</v>
       </c>
       <c r="C6" t="n">
-        <v>529869.6219776971</v>
+        <v>526809.8722720412</v>
       </c>
       <c r="D6" t="n">
-        <v>531420.0362200143</v>
+        <v>528360.2865143591</v>
       </c>
       <c r="E6" t="n">
-        <v>327609.7649146118</v>
+        <v>324578.6745675484</v>
       </c>
       <c r="F6" t="n">
-        <v>544352.2117857297</v>
+        <v>541321.1214386662</v>
       </c>
       <c r="G6" t="n">
-        <v>545896.7871756589</v>
+        <v>542255.3894631071</v>
       </c>
       <c r="H6" t="n">
-        <v>546843.0226934372</v>
+        <v>545309.9897552241</v>
       </c>
       <c r="I6" t="n">
-        <v>549899.7876487295</v>
+        <v>546862.7547105162</v>
       </c>
       <c r="J6" t="n">
-        <v>162613.3607172086</v>
+        <v>159026.7141951905</v>
       </c>
       <c r="K6" t="n">
-        <v>504274.0446949602</v>
+        <v>498911.2941461164</v>
       </c>
       <c r="L6" t="n">
-        <v>546604.3627073106</v>
+        <v>542841.6121584668</v>
       </c>
       <c r="M6" t="n">
-        <v>547336.8679588014</v>
+        <v>545174.1174099577</v>
       </c>
       <c r="N6" t="n">
-        <v>549671.5766980114</v>
+        <v>546708.8261491673</v>
       </c>
       <c r="O6" t="n">
-        <v>316901.6838531435</v>
+        <v>317048.0410141067</v>
       </c>
       <c r="P6" t="n">
-        <v>257643.4302542747</v>
+        <v>254689.1657766289</v>
       </c>
     </row>
   </sheetData>
@@ -26770,7 +26770,7 @@
         <v>269</v>
       </c>
       <c r="G2" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H2" t="n">
         <v>270</v>
@@ -26779,7 +26779,7 @@
         <v>270</v>
       </c>
       <c r="J2" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K2" t="n">
         <v>266</v>
@@ -26794,7 +26794,7 @@
         <v>266</v>
       </c>
       <c r="O2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -26874,7 +26874,7 @@
         <v>475</v>
       </c>
       <c r="G4" t="n">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="H4" t="n">
         <v>477</v>
@@ -26898,7 +26898,7 @@
         <v>452</v>
       </c>
       <c r="O4" t="n">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P4" t="n">
         <v>450</v>
@@ -26987,25 +26987,25 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>211</v>
+      </c>
+      <c r="K2" t="n">
+        <v>54</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>214</v>
-      </c>
-      <c r="K2" t="n">
-        <v>51</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27091,10 +27091,10 @@
         <v>-0</v>
       </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>-0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
@@ -27219,19 +27219,19 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -27332,10 +27332,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27445,13 +27445,13 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>399.6108044321707</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>118.464235059569</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>199.3629606373397</v>
       </c>
       <c r="S2" t="n">
-        <v>377.6703975017917</v>
+        <v>390.4592156497613</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,28 +27512,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.3007434221972</v>
       </c>
       <c r="H3" t="n">
         <v>327.9302758656664</v>
       </c>
       <c r="I3" t="n">
-        <v>202.0188387215372</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,31 +27557,31 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>117.0677933923664</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>400</v>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>400</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
       </c>
       <c r="X3" t="n">
-        <v>400</v>
+        <v>370.4207758456487</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27594,19 +27594,19 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>42.92693916918225</v>
       </c>
       <c r="G4" t="n">
-        <v>244.676003989071</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>225.5004375770285</v>
@@ -27624,19 +27624,19 @@
         <v>368.8555625840087</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N4" t="n">
         <v>400</v>
       </c>
       <c r="O4" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>400</v>
       </c>
       <c r="Q4" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -27657,10 +27657,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -27673,7 +27673,7 @@
         <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>215.7174602299046</v>
       </c>
       <c r="D5" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>399.6108044321707</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>199.3629606373397</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27752,10 +27752,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27764,13 +27764,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.3007434221972</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>202.0188387215372</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,10 +27794,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>117.0677933923664</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>45.03017465086985</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27806,16 +27806,16 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>154.8908499248819</v>
       </c>
       <c r="W6" t="n">
-        <v>383.7578432473442</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -27843,7 +27843,7 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>244.676003989071</v>
       </c>
       <c r="H7" t="n">
         <v>225.5004375770285</v>
@@ -27861,7 +27861,7 @@
         <v>368.8555625840087</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N7" t="n">
         <v>400</v>
@@ -27870,7 +27870,7 @@
         <v>400</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Q7" t="n">
         <v>400</v>
@@ -27891,7 +27891,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27925,10 +27925,10 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>399.6108044321707</v>
+        <v>354.0724265425064</v>
       </c>
       <c r="I8" t="n">
-        <v>118.464235059569</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>71.89462621654951</v>
+        <v>199.3629606373397</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27967,7 +27967,7 @@
         <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>400</v>
+        <v>154.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
@@ -27976,7 +27976,7 @@
         <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>36.31743268280638</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -27986,19 +27986,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>281.5801701892375</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.3007434221972</v>
@@ -28034,7 +28034,7 @@
         <v>117.0677933923664</v>
       </c>
       <c r="R9" t="n">
-        <v>45.03017465086985</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28046,16 +28046,16 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>95.7557111487493</v>
       </c>
     </row>
     <row r="10">
@@ -28065,22 +28065,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>244.676003989071</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>225.5004375770285</v>
@@ -28092,13 +28092,13 @@
         <v>9.260620967055303</v>
       </c>
       <c r="K10" t="n">
-        <v>245.7811016699955</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>368.8555625840087</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>396.6394382327288</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -28107,16 +28107,16 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>237.0713231966674</v>
       </c>
       <c r="T10" t="n">
         <v>208.4527632275692</v>
@@ -28134,7 +28134,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -28244,7 +28244,7 @@
         <v>269</v>
       </c>
       <c r="I12" t="n">
-        <v>202.0188387215372</v>
+        <v>269</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>208.7821347717676</v>
+        <v>141.8009734933051</v>
       </c>
       <c r="R12" t="n">
         <v>269</v>
@@ -28481,7 +28481,7 @@
         <v>269</v>
       </c>
       <c r="I15" t="n">
-        <v>202.0188387215372</v>
+        <v>269</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28496,7 +28496,7 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>91.71434137940128</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>117.0677933923664</v>
+        <v>141.8009734933051</v>
       </c>
       <c r="R15" t="n">
         <v>269</v>
@@ -28618,25 +28618,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I17" t="n">
         <v>118.464235059569</v>
@@ -28669,25 +28669,25 @@
         <v>199.3629606373397</v>
       </c>
       <c r="S17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="V17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="W17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="X17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y17" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18">
@@ -28697,25 +28697,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I18" t="n">
         <v>202.0188387215372</v>
@@ -28727,7 +28727,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>91.71434137940116</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -28742,31 +28742,31 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>117.0677933923664</v>
+        <v>193.4775740126613</v>
       </c>
       <c r="R18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="S18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="V18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="W18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="X18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y18" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19">
@@ -28776,76 +28776,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="S19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="T19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="V19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="W19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="X19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Y19" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20">
@@ -28958,7 +28958,7 @@
         <v>202.0188387215372</v>
       </c>
       <c r="J21" t="n">
-        <v>76.40978062029498</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>117.0677933923664</v>
+        <v>193.4775740126613</v>
       </c>
       <c r="R21" t="n">
         <v>270</v>
@@ -29192,10 +29192,10 @@
         <v>270</v>
       </c>
       <c r="I24" t="n">
-        <v>202.0188387215372</v>
+        <v>270</v>
       </c>
       <c r="J24" t="n">
-        <v>76.40978062029498</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>117.0677933923664</v>
+        <v>125.4964127341986</v>
       </c>
       <c r="R24" t="n">
         <v>270</v>
@@ -29329,25 +29329,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I26" t="n">
         <v>118.464235059569</v>
@@ -29380,25 +29380,25 @@
         <v>199.3629606373397</v>
       </c>
       <c r="S26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y26" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27">
@@ -29408,28 +29408,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I27" t="n">
-        <v>202.0188387215372</v>
+        <v>203.5747575411982</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29453,31 +29453,31 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>118.6237122120275</v>
+        <v>117.0677933923664</v>
       </c>
       <c r="R27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y27" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28">
@@ -29487,76 +29487,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="K28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="L28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="N28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="R28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="S28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="T28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="U28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="V28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="W28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Y28" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29">
@@ -29903,7 +29903,7 @@
         <v>266</v>
       </c>
       <c r="I33" t="n">
-        <v>202.0188387215372</v>
+        <v>203.5747575411982</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>118.6237122120275</v>
+        <v>117.0677933923664</v>
       </c>
       <c r="R33" t="n">
         <v>266</v>
@@ -30377,7 +30377,7 @@
         <v>266</v>
       </c>
       <c r="I39" t="n">
-        <v>203.5747575411982</v>
+        <v>202.0188387215372</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>117.0677933923664</v>
+        <v>118.6237122120275</v>
       </c>
       <c r="R39" t="n">
         <v>266</v>
@@ -30514,28 +30514,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,28 +30562,28 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="S41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="T41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="W41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="X41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Y41" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="42">
@@ -30593,34 +30593,34 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1.555918819660974</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -30638,31 +30638,31 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="S42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="T42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="W42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="X42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Y42" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43">
@@ -30672,76 +30672,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="L43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="P43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="R43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="S43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="T43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="U43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="V43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="W43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="X43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Y43" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44">
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>464.866735366192</v>
+        <v>34.5619987800353</v>
       </c>
       <c r="K11" t="n">
+        <v>474.9999999999999</v>
+      </c>
+      <c r="L11" t="n">
         <v>475</v>
       </c>
-      <c r="L11" t="n">
-        <v>129.4180100502514</v>
-      </c>
       <c r="M11" t="n">
-        <v>150.9490790767628</v>
+        <v>475</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>235.6718257131709</v>
       </c>
       <c r="O11" t="n">
         <v>67.92983896862111</v>
@@ -35475,7 +35475,7 @@
         <v>117.6444173462533</v>
       </c>
       <c r="Q11" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,7 +35530,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>66.98116127846279</v>
       </c>
       <c r="J12" t="n">
         <v>166.6648703886191</v>
@@ -35554,7 +35554,7 @@
         <v>197.4561177222004</v>
       </c>
       <c r="Q12" t="n">
-        <v>91.71434137940122</v>
+        <v>24.73318010093872</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35703,7 +35703,7 @@
         <v>475</v>
       </c>
       <c r="N14" t="n">
-        <v>46.62921978028059</v>
+        <v>475</v>
       </c>
       <c r="O14" t="n">
         <v>67.92983896862111</v>
@@ -35712,7 +35712,7 @@
         <v>117.6444173462533</v>
       </c>
       <c r="Q14" t="n">
-        <v>475</v>
+        <v>46.62921978028059</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35767,7 +35767,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>66.98116127846279</v>
       </c>
       <c r="J15" t="n">
         <v>166.6648703886191</v>
@@ -35782,7 +35782,7 @@
         <v>198.1300421645042</v>
       </c>
       <c r="N15" t="n">
-        <v>340.463495261641</v>
+        <v>248.7491538822397</v>
       </c>
       <c r="O15" t="n">
         <v>345.8569086951992</v>
@@ -35791,7 +35791,7 @@
         <v>197.4561177222004</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>24.73318010093872</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>34.5619987800353</v>
+        <v>464.866735366192</v>
       </c>
       <c r="K17" t="n">
-        <v>474.9999999999999</v>
+        <v>477</v>
       </c>
       <c r="L17" t="n">
-        <v>129.4180100502513</v>
+        <v>129.4180100502514</v>
       </c>
       <c r="M17" t="n">
-        <v>475</v>
+        <v>154.8682709959548</v>
       </c>
       <c r="N17" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>67.92983896862111</v>
@@ -35949,7 +35949,7 @@
         <v>117.6444173462533</v>
       </c>
       <c r="Q17" t="n">
-        <v>106.2538156629198</v>
+        <v>477</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36013,7 +36013,7 @@
         <v>261.9592131313574</v>
       </c>
       <c r="L18" t="n">
-        <v>461.0794903129938</v>
+        <v>369.3651489335926</v>
       </c>
       <c r="M18" t="n">
         <v>198.1300421645042</v>
@@ -36028,7 +36028,7 @@
         <v>197.4561177222004</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>76.40978062029492</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36077,19 +36077,19 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>24.32399601092898</v>
+        <v>25.32399601092898</v>
       </c>
       <c r="H19" t="n">
-        <v>43.49956242297154</v>
+        <v>44.49956242297154</v>
       </c>
       <c r="I19" t="n">
-        <v>103.4293640520129</v>
+        <v>104.4293640520129</v>
       </c>
       <c r="J19" t="n">
-        <v>259.7393790329447</v>
+        <v>260.7393790329447</v>
       </c>
       <c r="K19" t="n">
-        <v>23.21889833000449</v>
+        <v>24.21889833000449</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36116,19 +36116,19 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>60.54723677243081</v>
+        <v>61.54723677243081</v>
       </c>
       <c r="U19" t="n">
-        <v>118.0616742993126</v>
+        <v>119.0616742993126</v>
       </c>
       <c r="V19" t="n">
-        <v>69.82968978378381</v>
+        <v>70.82968978378381</v>
       </c>
       <c r="W19" t="n">
-        <v>42.62719016129032</v>
+        <v>43.62719016129032</v>
       </c>
       <c r="X19" t="n">
-        <v>21.55635456989245</v>
+        <v>22.55635456989245</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -36165,10 +36165,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>464.866735366192</v>
+        <v>34.5619987800353</v>
       </c>
       <c r="K20" t="n">
-        <v>104.3198592964824</v>
+        <v>476.9999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>129.4180100502513</v>
@@ -36177,16 +36177,16 @@
         <v>477</v>
       </c>
       <c r="N20" t="n">
-        <v>50.54841169947238</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>67.92983896862111</v>
+        <v>477</v>
       </c>
       <c r="P20" t="n">
         <v>117.6444173462533</v>
       </c>
       <c r="Q20" t="n">
-        <v>477</v>
+        <v>176.1028465507328</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36244,7 +36244,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>243.0746510089141</v>
+        <v>166.6648703886191</v>
       </c>
       <c r="K21" t="n">
         <v>261.9592131313574</v>
@@ -36265,7 +36265,7 @@
         <v>197.4561177222004</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>76.40978062029492</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36402,10 +36402,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>464.866735366192</v>
+        <v>34.5619987800353</v>
       </c>
       <c r="K23" t="n">
-        <v>104.3198592964824</v>
+        <v>476.9999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>129.4180100502513</v>
@@ -36414,7 +36414,7 @@
         <v>477</v>
       </c>
       <c r="N23" t="n">
-        <v>50.54841169947238</v>
+        <v>108.1730075821116</v>
       </c>
       <c r="O23" t="n">
         <v>67.92983896862111</v>
@@ -36478,10 +36478,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>67.98116127846279</v>
       </c>
       <c r="J24" t="n">
-        <v>243.0746510089141</v>
+        <v>166.6648703886191</v>
       </c>
       <c r="K24" t="n">
         <v>261.9592131313574</v>
@@ -36502,7 +36502,7 @@
         <v>197.4561177222004</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>8.428619341832174</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36551,7 +36551,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>25.32399601092899</v>
+        <v>25.32399601092898</v>
       </c>
       <c r="H25" t="n">
         <v>44.49956242297154</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>34.5619987800353</v>
+        <v>452.0000000000013</v>
       </c>
       <c r="K26" t="n">
         <v>104.3198592964824</v>
       </c>
       <c r="L26" t="n">
-        <v>129.4180100502512</v>
+        <v>211.7730970946344</v>
       </c>
       <c r="M26" t="n">
-        <v>431.8632492957302</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>452</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>67.92983896862111</v>
+        <v>452.0000000000013</v>
       </c>
       <c r="P26" t="n">
         <v>117.6444173462533</v>
       </c>
       <c r="Q26" t="n">
-        <v>452</v>
+        <v>452.0000000000013</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1.555918819660929</v>
       </c>
       <c r="J27" t="n">
         <v>166.6648703886191</v>
@@ -36739,7 +36739,7 @@
         <v>197.4561177222004</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.555918819661137</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36794,10 +36794,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>49.42936405201289</v>
+        <v>46.42936405201289</v>
       </c>
       <c r="J28" t="n">
-        <v>205.7393790329447</v>
+        <v>202.7393790329447</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -36827,13 +36827,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>6.547236772430807</v>
+        <v>3.547236772430807</v>
       </c>
       <c r="U28" t="n">
-        <v>64.06167429931256</v>
+        <v>61.06167429931256</v>
       </c>
       <c r="V28" t="n">
-        <v>15.82968978378381</v>
+        <v>12.82968978378381</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -36879,16 +36879,16 @@
         <v>34.5619987800353</v>
       </c>
       <c r="K29" t="n">
-        <v>452</v>
+        <v>104.3198592964824</v>
       </c>
       <c r="L29" t="n">
         <v>452</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>452.0000000000013</v>
       </c>
       <c r="N29" t="n">
-        <v>452</v>
+        <v>452.0000000000013</v>
       </c>
       <c r="O29" t="n">
         <v>67.92983896862111</v>
@@ -36897,7 +36897,7 @@
         <v>117.6444173462533</v>
       </c>
       <c r="Q29" t="n">
-        <v>213.6011186424639</v>
+        <v>109.281259345979</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37025,7 +37025,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>21.32399601092899</v>
+        <v>21.32399601092898</v>
       </c>
       <c r="H31" t="n">
         <v>40.49956242297154</v>
@@ -37113,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>452</v>
+        <v>34.5619987800353</v>
       </c>
       <c r="K32" t="n">
-        <v>452.0000000000001</v>
+        <v>104.3198592964824</v>
       </c>
       <c r="L32" t="n">
-        <v>129.4180100502513</v>
+        <v>129.4180100502512</v>
       </c>
       <c r="M32" t="n">
-        <v>452</v>
+        <v>452.0000000000014</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>431.8632492957275</v>
       </c>
       <c r="O32" t="n">
         <v>67.92983896862111</v>
@@ -37134,7 +37134,7 @@
         <v>117.6444173462533</v>
       </c>
       <c r="Q32" t="n">
-        <v>118.7451073722477</v>
+        <v>452.0000000000014</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1.555918819660929</v>
       </c>
       <c r="J33" t="n">
         <v>166.6648703886191</v>
@@ -37213,7 +37213,7 @@
         <v>197.4561177222004</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.555918819661137</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37353,16 +37353,16 @@
         <v>34.5619987800353</v>
       </c>
       <c r="K35" t="n">
-        <v>104.3198592964824</v>
+        <v>452</v>
       </c>
       <c r="L35" t="n">
-        <v>129.4180100502512</v>
+        <v>129.4180100502513</v>
       </c>
       <c r="M35" t="n">
-        <v>452</v>
+        <v>452.0000000000014</v>
       </c>
       <c r="N35" t="n">
-        <v>431.8632492957302</v>
+        <v>84.18310859220982</v>
       </c>
       <c r="O35" t="n">
         <v>67.92983896862111</v>
@@ -37371,7 +37371,7 @@
         <v>117.6444173462533</v>
       </c>
       <c r="Q35" t="n">
-        <v>452</v>
+        <v>452.0000000000014</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37499,7 +37499,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>21.32399601092898</v>
+        <v>21.32399601092899</v>
       </c>
       <c r="H37" t="n">
         <v>40.49956242297154</v>
@@ -37587,7 +37587,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>452</v>
+        <v>452.0000000000014</v>
       </c>
       <c r="K38" t="n">
         <v>104.3198592964824</v>
@@ -37596,19 +37596,19 @@
         <v>129.4180100502513</v>
       </c>
       <c r="M38" t="n">
-        <v>452</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>14.42524807576554</v>
+        <v>452.0000000000014</v>
       </c>
       <c r="O38" t="n">
         <v>67.92983896862111</v>
       </c>
       <c r="P38" t="n">
-        <v>117.6444173462533</v>
+        <v>452.0000000000014</v>
       </c>
       <c r="Q38" t="n">
-        <v>452</v>
+        <v>132.0696654220148</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37663,7 +37663,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1.555918819660929</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>166.6648703886191</v>
@@ -37687,7 +37687,7 @@
         <v>197.4561177222004</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.555918819661137</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37736,7 +37736,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>21.32399601092898</v>
+        <v>21.32399601092899</v>
       </c>
       <c r="H40" t="n">
         <v>40.49956242297154</v>
@@ -37824,7 +37824,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>452</v>
+        <v>450.0000000000015</v>
       </c>
       <c r="K41" t="n">
         <v>104.3198592964824</v>
@@ -37833,19 +37833,19 @@
         <v>129.4180100502513</v>
       </c>
       <c r="M41" t="n">
-        <v>452</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>14.42524807576554</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>67.92983896862111</v>
+        <v>198.0803124714437</v>
       </c>
       <c r="P41" t="n">
-        <v>117.6444173462533</v>
+        <v>450.0000000000015</v>
       </c>
       <c r="Q41" t="n">
-        <v>452</v>
+        <v>450.0000000000015</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37906,7 +37906,7 @@
         <v>166.6648703886191</v>
       </c>
       <c r="K42" t="n">
-        <v>263.5151319510183</v>
+        <v>261.9592131313574</v>
       </c>
       <c r="L42" t="n">
         <v>369.3651489335926</v>
@@ -37921,7 +37921,7 @@
         <v>345.8569086951992</v>
       </c>
       <c r="P42" t="n">
-        <v>197.4561177222004</v>
+        <v>191.0928446226696</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>42.7393790329447</v>
+        <v>45.7393790329447</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38073,7 +38073,7 @@
         <v>450</v>
       </c>
       <c r="N44" t="n">
-        <v>450</v>
+        <v>427.9440573765383</v>
       </c>
       <c r="O44" t="n">
         <v>67.92983896862111</v>
@@ -38082,7 +38082,7 @@
         <v>117.6444173462533</v>
       </c>
       <c r="Q44" t="n">
-        <v>427.9440573765382</v>
+        <v>450</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,7 +38143,7 @@
         <v>166.6648703886191</v>
       </c>
       <c r="K45" t="n">
-        <v>255.5959400318264</v>
+        <v>261.9592131313574</v>
       </c>
       <c r="L45" t="n">
         <v>369.3651489335926</v>
@@ -38152,7 +38152,7 @@
         <v>198.1300421645042</v>
       </c>
       <c r="N45" t="n">
-        <v>248.7491538822397</v>
+        <v>242.3858807827087</v>
       </c>
       <c r="O45" t="n">
         <v>345.8569086951992</v>
